--- a/data/output/sim_gridrnd/REL2/group_500_40/results/REL2_G5_results_summary.xlsx
+++ b/data/output/sim_gridrnd/REL2/group_500_40/results/REL2_G5_results_summary.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB23"/>
+  <dimension ref="A1:CM23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,24 +436,24 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>mu</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>sigma</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>jnd</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>pse</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>jnd</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>sigma</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>mu</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>n_trials</t>
@@ -466,1106 +466,1260 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>lat_entropy_100</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_120</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_140</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_160</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_180</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_200</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_40</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_60</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_80</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>model</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>pse_40</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>jnd_40</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>pse_60</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>jnd_60</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>pse_80</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>jnd_80</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>pse_100</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>jnd_100</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>pse_120</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>jnd_120</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>pse_140</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>jnd_140</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>pse_160</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>jnd_160</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>pse_180</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>jnd_180</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>pse_200</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>jnd_200</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_40</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_60</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_80</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_100</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_120</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_140</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_160</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_180</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_200</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_40</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_60</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_80</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_100</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_120</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_140</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_160</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_180</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_200</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_40</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_60</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_80</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_100</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_120</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_140</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_160</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_180</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_200</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_40</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_60</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_80</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_100</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_120</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_140</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_160</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_180</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_200</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_40</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_60</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_80</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_100</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_120</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_140</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_160</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_180</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_200</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_40</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_60</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_80</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_100</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_120</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_140</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_160</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_180</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_200</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>pse_est</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>jnd_est</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S02_G5_498_39_REL2</t>
+          <t>S01_G5_499_40_REL2</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C2" t="n">
-        <v>39</v>
+        <v>59.30318754633062</v>
       </c>
       <c r="D2" t="n">
-        <v>57.82060785767235</v>
+        <v>40</v>
       </c>
       <c r="E2" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="F2" t="n">
         <v>200</v>
       </c>
       <c r="G2" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="H2" t="inlineStr">
+        <v>81.5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I2" t="n">
-        <v>501.7590688009498</v>
-      </c>
-      <c r="J2" t="n">
-        <v>57.44515998346411</v>
-      </c>
-      <c r="K2" t="n">
-        <v>492.848196490663</v>
-      </c>
-      <c r="L2" t="n">
-        <v>47.70114940340776</v>
-      </c>
-      <c r="M2" t="n">
-        <v>501.8560326078611</v>
-      </c>
-      <c r="N2" t="n">
-        <v>54.90446570585031</v>
-      </c>
-      <c r="O2" t="n">
-        <v>497.3520938304029</v>
-      </c>
-      <c r="P2" t="n">
-        <v>52.88318144805807</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>500.88163783647</v>
-      </c>
       <c r="R2" t="n">
-        <v>49.91916329228825</v>
+        <v>479.41</v>
       </c>
       <c r="S2" t="n">
-        <v>493.7146249880333</v>
+        <v>25.88</v>
       </c>
       <c r="T2" t="n">
-        <v>53.19726496528321</v>
+        <v>494.12</v>
       </c>
       <c r="U2" t="n">
-        <v>490.1372975636678</v>
+        <v>29.05</v>
       </c>
       <c r="V2" t="n">
-        <v>55.96241191971373</v>
+        <v>498.34</v>
       </c>
       <c r="W2" t="n">
-        <v>489.4593974851185</v>
+        <v>31.78</v>
       </c>
       <c r="X2" t="n">
-        <v>56.55328219901889</v>
+        <v>496.72</v>
       </c>
       <c r="Y2" t="n">
-        <v>494.5235601449639</v>
+        <v>35.53</v>
       </c>
       <c r="Z2" t="n">
-        <v>56.99369611580362</v>
+        <v>496.32</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>36.95</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>495.89</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>37.95</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>500.51</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>45.28</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>498.59</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>43.84</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>496.96</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>42.66</v>
       </c>
       <c r="AJ2" t="n">
-        <v>501.6</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>497.7666666666667</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>497.95</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>499.3</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>499.7416666666667</v>
+        <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>498.3214285714286</v>
+        <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>493.7125</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>489.1444444444444</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>488.085</v>
+        <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>79.92521504506571</v>
+        <v>482.75</v>
       </c>
       <c r="AT2" t="n">
-        <v>76.24464279905543</v>
+        <v>484.9333333333333</v>
       </c>
       <c r="AU2" t="n">
-        <v>71.85678464835455</v>
+        <v>488.95</v>
       </c>
       <c r="AV2" t="n">
-        <v>68.56770376788185</v>
+        <v>490.58</v>
       </c>
       <c r="AW2" t="n">
-        <v>66.16299265618373</v>
+        <v>488.9666666666666</v>
       </c>
       <c r="AX2" t="n">
-        <v>65.38318567787711</v>
+        <v>489.1714285714286</v>
       </c>
       <c r="AY2" t="n">
-        <v>67.38493781068586</v>
+        <v>490.31875</v>
       </c>
       <c r="AZ2" t="n">
-        <v>68.97850890935543</v>
+        <v>494.7666666666667</v>
       </c>
       <c r="BA2" t="n">
-        <v>68.96562748935153</v>
+        <v>497.94</v>
       </c>
       <c r="BB2" t="n">
-        <v>340</v>
+        <v>75.14777109136371</v>
       </c>
       <c r="BC2" t="n">
-        <v>340</v>
+        <v>63.98668264221514</v>
       </c>
       <c r="BD2" t="n">
-        <v>340</v>
+        <v>58.87527070001462</v>
       </c>
       <c r="BE2" t="n">
-        <v>340</v>
+        <v>55.65575980974476</v>
       </c>
       <c r="BF2" t="n">
-        <v>340</v>
+        <v>55.83202983553039</v>
       </c>
       <c r="BG2" t="n">
-        <v>340</v>
+        <v>57.84905763612537</v>
       </c>
       <c r="BH2" t="n">
-        <v>340</v>
+        <v>60.35575489079314</v>
       </c>
       <c r="BI2" t="n">
-        <v>340</v>
+        <v>61.96550115454028</v>
       </c>
       <c r="BJ2" t="n">
-        <v>340</v>
+        <v>61.65489761568013</v>
       </c>
       <c r="BK2" t="n">
-        <v>669</v>
+        <v>324</v>
       </c>
       <c r="BL2" t="n">
-        <v>669</v>
+        <v>324</v>
       </c>
       <c r="BM2" t="n">
-        <v>669</v>
+        <v>324</v>
       </c>
       <c r="BN2" t="n">
-        <v>669</v>
+        <v>324</v>
       </c>
       <c r="BO2" t="n">
-        <v>669</v>
+        <v>324</v>
       </c>
       <c r="BP2" t="n">
-        <v>669</v>
+        <v>324</v>
       </c>
       <c r="BQ2" t="n">
-        <v>669</v>
+        <v>324</v>
       </c>
       <c r="BR2" t="n">
-        <v>669</v>
+        <v>324</v>
       </c>
       <c r="BS2" t="n">
-        <v>669</v>
+        <v>324</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.7777777777777778</v>
+        <v>669</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.8666666666666667</v>
+        <v>669</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.7619047619047619</v>
+        <v>669</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.5333333333333333</v>
+        <v>669</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.4848484848484849</v>
+        <v>669</v>
       </c>
       <c r="BY2" t="n">
-        <v>0</v>
+        <v>669</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0</v>
+        <v>669</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>669</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.4848484848484849</v>
+        <v>669</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>0.7333333333333333</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>0.6785714285714286</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>496.96</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>42.66</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S03_G5_501_41_REL2</t>
+          <t>S02_G5_498_39_REL2</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="C3" t="n">
-        <v>41</v>
+        <v>57.82060785767235</v>
       </c>
       <c r="D3" t="n">
-        <v>60.78576723498888</v>
+        <v>39</v>
       </c>
       <c r="E3" t="n">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="F3" t="n">
         <v>200</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H3" t="inlineStr">
+        <v>79.5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I3" t="n">
-        <v>476.8602956578414</v>
-      </c>
-      <c r="J3" t="n">
-        <v>44.38375514893274</v>
-      </c>
-      <c r="K3" t="n">
-        <v>480.3043982754357</v>
-      </c>
-      <c r="L3" t="n">
-        <v>51.45500065598331</v>
-      </c>
-      <c r="M3" t="n">
-        <v>480.6383609259676</v>
-      </c>
-      <c r="N3" t="n">
-        <v>44.84395645781927</v>
-      </c>
-      <c r="O3" t="n">
-        <v>483.2723843363862</v>
-      </c>
-      <c r="P3" t="n">
-        <v>46.98217391279196</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>488.6450328361921</v>
-      </c>
       <c r="R3" t="n">
-        <v>61.6007527117275</v>
+        <v>501.76</v>
       </c>
       <c r="S3" t="n">
-        <v>492.9605868343153</v>
+        <v>57.45</v>
       </c>
       <c r="T3" t="n">
-        <v>56.78652432926754</v>
+        <v>492.85</v>
       </c>
       <c r="U3" t="n">
-        <v>492.6040326768095</v>
+        <v>47.7</v>
       </c>
       <c r="V3" t="n">
-        <v>54.88742406786745</v>
+        <v>501.86</v>
       </c>
       <c r="W3" t="n">
-        <v>492.2335454406398</v>
+        <v>54.9</v>
       </c>
       <c r="X3" t="n">
-        <v>50.90872008013465</v>
+        <v>497.35</v>
       </c>
       <c r="Y3" t="n">
-        <v>492.1471420471978</v>
+        <v>52.88</v>
       </c>
       <c r="Z3" t="n">
-        <v>49.7555761199169</v>
+        <v>500.88</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>49.92</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>493.71</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>53.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>490.14</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>55.96</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>489.46</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>56.55</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>494.52</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>56.99</v>
       </c>
       <c r="AJ3" t="n">
-        <v>490.05</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>484.9333333333333</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>483.825</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>483.29</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>484.4083333333334</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>488.1928571428571</v>
+        <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>490.29375</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>491.8444444444444</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>493.01</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>76.25678658322811</v>
+        <v>501.6</v>
       </c>
       <c r="AT3" t="n">
-        <v>71.16128785293931</v>
+        <v>497.7666666666667</v>
       </c>
       <c r="AU3" t="n">
-        <v>67.35331747583039</v>
+        <v>497.95</v>
       </c>
       <c r="AV3" t="n">
-        <v>64.58626711616023</v>
+        <v>499.3</v>
       </c>
       <c r="AW3" t="n">
-        <v>63.4068208519837</v>
+        <v>499.7416666666667</v>
       </c>
       <c r="AX3" t="n">
-        <v>65.98548503037526</v>
+        <v>498.3214285714286</v>
       </c>
       <c r="AY3" t="n">
-        <v>66.23901766283601</v>
+        <v>493.7125</v>
       </c>
       <c r="AZ3" t="n">
-        <v>66.22686784599857</v>
+        <v>489.1444444444444</v>
       </c>
       <c r="BA3" t="n">
-        <v>65.19524445847259</v>
+        <v>488.085</v>
       </c>
       <c r="BB3" t="n">
-        <v>321</v>
+        <v>79.92521504506571</v>
       </c>
       <c r="BC3" t="n">
-        <v>321</v>
+        <v>76.24464279905543</v>
       </c>
       <c r="BD3" t="n">
-        <v>321</v>
+        <v>71.85678464835455</v>
       </c>
       <c r="BE3" t="n">
-        <v>321</v>
+        <v>68.56770376788185</v>
       </c>
       <c r="BF3" t="n">
-        <v>321</v>
+        <v>66.16299265618373</v>
       </c>
       <c r="BG3" t="n">
-        <v>321</v>
+        <v>65.38318567787711</v>
       </c>
       <c r="BH3" t="n">
-        <v>321</v>
+        <v>67.38493781068586</v>
       </c>
       <c r="BI3" t="n">
-        <v>321</v>
+        <v>68.97850890935543</v>
       </c>
       <c r="BJ3" t="n">
-        <v>321</v>
+        <v>68.96562748935153</v>
       </c>
       <c r="BK3" t="n">
-        <v>669</v>
+        <v>340</v>
       </c>
       <c r="BL3" t="n">
-        <v>669</v>
+        <v>340</v>
       </c>
       <c r="BM3" t="n">
-        <v>669</v>
+        <v>340</v>
       </c>
       <c r="BN3" t="n">
-        <v>669</v>
+        <v>340</v>
       </c>
       <c r="BO3" t="n">
-        <v>669</v>
+        <v>340</v>
       </c>
       <c r="BP3" t="n">
-        <v>669</v>
+        <v>340</v>
       </c>
       <c r="BQ3" t="n">
-        <v>669</v>
+        <v>340</v>
       </c>
       <c r="BR3" t="n">
-        <v>669</v>
+        <v>340</v>
       </c>
       <c r="BS3" t="n">
-        <v>669</v>
+        <v>340</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.6</v>
+        <v>669</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.625</v>
+        <v>669</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.5769230769230769</v>
+        <v>669</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.5555555555555556</v>
+        <v>669</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.5238095238095238</v>
+        <v>669</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.6666666666666666</v>
+        <v>669</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.8095238095238095</v>
+        <v>669</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.9047619047619048</v>
+        <v>669</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.9523809523809523</v>
+        <v>669</v>
+      </c>
+      <c r="CC3" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="CD3" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="CE3" t="n">
+        <v>0.7619047619047619</v>
+      </c>
+      <c r="CF3" t="n">
+        <v>0.5333333333333333</v>
+      </c>
+      <c r="CG3" t="n">
+        <v>0.4848484848484849</v>
+      </c>
+      <c r="CH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK3" t="n">
+        <v>0.4848484848484849</v>
+      </c>
+      <c r="CL3" t="n">
+        <v>494.52</v>
+      </c>
+      <c r="CM3" t="n">
+        <v>56.99</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S01_G5_499_40_REL2</t>
+          <t>S03_G5_501_41_REL2</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C4" t="n">
-        <v>40</v>
+        <v>60.78576723498888</v>
       </c>
       <c r="D4" t="n">
-        <v>59.30318754633062</v>
+        <v>41</v>
       </c>
       <c r="E4" t="n">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="F4" t="n">
         <v>200</v>
       </c>
       <c r="G4" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="H4" t="inlineStr">
+        <v>81</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I4" t="n">
-        <v>479.4128848427479</v>
-      </c>
-      <c r="J4" t="n">
-        <v>25.87829585602786</v>
-      </c>
-      <c r="K4" t="n">
-        <v>494.1162541998953</v>
-      </c>
-      <c r="L4" t="n">
-        <v>29.05011903615937</v>
-      </c>
-      <c r="M4" t="n">
-        <v>498.3421393559365</v>
-      </c>
-      <c r="N4" t="n">
-        <v>31.78080624608705</v>
-      </c>
-      <c r="O4" t="n">
-        <v>496.7177697159162</v>
-      </c>
-      <c r="P4" t="n">
-        <v>35.52601829282189</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>496.3234107084786</v>
-      </c>
       <c r="R4" t="n">
-        <v>36.95060494734721</v>
+        <v>476.86</v>
       </c>
       <c r="S4" t="n">
-        <v>495.8884696448165</v>
+        <v>44.38</v>
       </c>
       <c r="T4" t="n">
-        <v>37.948856461247</v>
+        <v>480.3</v>
       </c>
       <c r="U4" t="n">
-        <v>500.509741870133</v>
+        <v>51.46</v>
       </c>
       <c r="V4" t="n">
-        <v>45.27613536305935</v>
+        <v>480.64</v>
       </c>
       <c r="W4" t="n">
-        <v>498.5906786658604</v>
+        <v>44.84</v>
       </c>
       <c r="X4" t="n">
-        <v>43.83957587404374</v>
+        <v>483.27</v>
       </c>
       <c r="Y4" t="n">
-        <v>496.9646793490936</v>
+        <v>46.98</v>
       </c>
       <c r="Z4" t="n">
-        <v>42.65795247350349</v>
+        <v>488.65</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>61.6</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>492.96</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>56.79</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>492.6</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>54.89</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>492.23</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>50.91</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>492.15</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>49.76</v>
       </c>
       <c r="AJ4" t="n">
-        <v>482.75</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>490.05</v>
+      </c>
+      <c r="AT4" t="n">
         <v>484.9333333333333</v>
       </c>
-      <c r="AL4" t="n">
-        <v>488.95</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>490.58</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>488.9666666666666</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>489.1714285714286</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>490.31875</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>494.7666666666667</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>497.94</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>75.14777109136371</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>63.98668264221514</v>
-      </c>
       <c r="AU4" t="n">
-        <v>58.87527070001462</v>
+        <v>483.825</v>
       </c>
       <c r="AV4" t="n">
-        <v>55.65575980974476</v>
+        <v>483.29</v>
       </c>
       <c r="AW4" t="n">
-        <v>55.83202983553039</v>
+        <v>484.4083333333334</v>
       </c>
       <c r="AX4" t="n">
-        <v>57.84905763612537</v>
+        <v>488.1928571428571</v>
       </c>
       <c r="AY4" t="n">
-        <v>60.35575489079314</v>
+        <v>490.29375</v>
       </c>
       <c r="AZ4" t="n">
-        <v>61.96550115454028</v>
+        <v>491.8444444444444</v>
       </c>
       <c r="BA4" t="n">
-        <v>61.65489761568013</v>
+        <v>493.01</v>
       </c>
       <c r="BB4" t="n">
-        <v>324</v>
+        <v>76.25678658322811</v>
       </c>
       <c r="BC4" t="n">
-        <v>324</v>
+        <v>71.16128785293931</v>
       </c>
       <c r="BD4" t="n">
-        <v>324</v>
+        <v>67.35331747583039</v>
       </c>
       <c r="BE4" t="n">
-        <v>324</v>
+        <v>64.58626711616023</v>
       </c>
       <c r="BF4" t="n">
-        <v>324</v>
+        <v>63.4068208519837</v>
       </c>
       <c r="BG4" t="n">
-        <v>324</v>
+        <v>65.98548503037526</v>
       </c>
       <c r="BH4" t="n">
-        <v>324</v>
+        <v>66.23901766283601</v>
       </c>
       <c r="BI4" t="n">
-        <v>324</v>
+        <v>66.22686784599857</v>
       </c>
       <c r="BJ4" t="n">
-        <v>324</v>
+        <v>65.19524445847259</v>
       </c>
       <c r="BK4" t="n">
-        <v>669</v>
+        <v>321</v>
       </c>
       <c r="BL4" t="n">
-        <v>669</v>
+        <v>321</v>
       </c>
       <c r="BM4" t="n">
-        <v>669</v>
+        <v>321</v>
       </c>
       <c r="BN4" t="n">
-        <v>669</v>
+        <v>321</v>
       </c>
       <c r="BO4" t="n">
-        <v>669</v>
+        <v>321</v>
       </c>
       <c r="BP4" t="n">
-        <v>669</v>
+        <v>321</v>
       </c>
       <c r="BQ4" t="n">
-        <v>669</v>
+        <v>321</v>
       </c>
       <c r="BR4" t="n">
-        <v>669</v>
+        <v>321</v>
       </c>
       <c r="BS4" t="n">
-        <v>669</v>
+        <v>321</v>
       </c>
       <c r="BT4" t="n">
-        <v>1</v>
+        <v>669</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.7333333333333333</v>
+        <v>669</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.875</v>
+        <v>669</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.8</v>
+        <v>669</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.5714285714285714</v>
+        <v>669</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.6785714285714286</v>
+        <v>669</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.7142857142857143</v>
+        <v>669</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.75</v>
+        <v>669</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.7857142857142857</v>
+        <v>669</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>0.5769230769230769</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>0.5238095238095238</v>
+      </c>
+      <c r="CH4" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>0.8095238095238095</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>0.9047619047619048</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>0.9523809523809523</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>492.15</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>49.76</v>
       </c>
     </row>
     <row r="5">
@@ -1578,10 +1732,10 @@
         <v>500</v>
       </c>
       <c r="C5" t="n">
+        <v>62.26834692364714</v>
+      </c>
+      <c r="D5" t="n">
         <v>42</v>
-      </c>
-      <c r="D5" t="n">
-        <v>62.26834692364714</v>
       </c>
       <c r="E5" t="n">
         <v>500</v>
@@ -1590,228 +1744,261 @@
         <v>200</v>
       </c>
       <c r="G5" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="H5" t="inlineStr">
+        <v>78</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I5" t="n">
-        <v>505.0095816015553</v>
-      </c>
-      <c r="J5" t="n">
-        <v>37.70857628149901</v>
-      </c>
-      <c r="K5" t="n">
-        <v>493.6330089323714</v>
-      </c>
-      <c r="L5" t="n">
-        <v>41.7615325546923</v>
-      </c>
-      <c r="M5" t="n">
-        <v>493.0165816379682</v>
-      </c>
-      <c r="N5" t="n">
-        <v>42.86863808713154</v>
-      </c>
-      <c r="O5" t="n">
-        <v>499.3226697381843</v>
-      </c>
-      <c r="P5" t="n">
-        <v>42.55446286875527</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>496.1955008222739</v>
-      </c>
       <c r="R5" t="n">
-        <v>43.94066280483815</v>
+        <v>505.01</v>
       </c>
       <c r="S5" t="n">
-        <v>496.0334984153648</v>
+        <v>37.71</v>
       </c>
       <c r="T5" t="n">
-        <v>44.14445980604012</v>
+        <v>493.63</v>
       </c>
       <c r="U5" t="n">
-        <v>493.453758349786</v>
+        <v>41.76</v>
       </c>
       <c r="V5" t="n">
-        <v>50.34802121789934</v>
+        <v>493.02</v>
       </c>
       <c r="W5" t="n">
-        <v>492.9057970657871</v>
+        <v>42.87</v>
       </c>
       <c r="X5" t="n">
-        <v>53.48701688664036</v>
+        <v>499.32</v>
       </c>
       <c r="Y5" t="n">
-        <v>494.1241115863209</v>
+        <v>42.55</v>
       </c>
       <c r="Z5" t="n">
-        <v>54.62833952696598</v>
+        <v>496.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>43.94</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>496.03</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>44.14</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>493.45</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>50.35</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>492.91</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>53.49</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>494.12</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>54.63</v>
       </c>
       <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
         <v>491.5</v>
       </c>
-      <c r="AK5" t="n">
+      <c r="AT5" t="n">
         <v>493.7333333333333</v>
       </c>
-      <c r="AL5" t="n">
+      <c r="AU5" t="n">
         <v>493.075</v>
       </c>
-      <c r="AM5" t="n">
+      <c r="AV5" t="n">
         <v>494.4</v>
       </c>
-      <c r="AN5" t="n">
+      <c r="AW5" t="n">
         <v>495.75</v>
       </c>
-      <c r="AO5" t="n">
+      <c r="AX5" t="n">
         <v>495.4928571428571</v>
       </c>
-      <c r="AP5" t="n">
+      <c r="AY5" t="n">
         <v>494.2125</v>
       </c>
-      <c r="AQ5" t="n">
+      <c r="AZ5" t="n">
         <v>491.8111111111111</v>
       </c>
-      <c r="AR5" t="n">
+      <c r="BA5" t="n">
         <v>490.285</v>
       </c>
-      <c r="AS5" t="n">
+      <c r="BB5" t="n">
         <v>76.7749959296645</v>
       </c>
-      <c r="AT5" t="n">
+      <c r="BC5" t="n">
         <v>69.01035349053711</v>
       </c>
-      <c r="AU5" t="n">
+      <c r="BD5" t="n">
         <v>64.53541179073704</v>
       </c>
-      <c r="AV5" t="n">
+      <c r="BE5" t="n">
         <v>61.17450449329361</v>
       </c>
-      <c r="AW5" t="n">
+      <c r="BF5" t="n">
         <v>58.63947049556297</v>
       </c>
-      <c r="AX5" t="n">
+      <c r="BG5" t="n">
         <v>57.37937613918827</v>
       </c>
-      <c r="AY5" t="n">
+      <c r="BH5" t="n">
         <v>57.94430380762203</v>
       </c>
-      <c r="AZ5" t="n">
+      <c r="BI5" t="n">
         <v>59.68172890786676</v>
       </c>
-      <c r="BA5" t="n">
+      <c r="BJ5" t="n">
         <v>61.21841042529609</v>
       </c>
-      <c r="BB5" t="n">
+      <c r="BK5" t="n">
         <v>330</v>
       </c>
-      <c r="BC5" t="n">
+      <c r="BL5" t="n">
         <v>330</v>
       </c>
-      <c r="BD5" t="n">
+      <c r="BM5" t="n">
         <v>330</v>
       </c>
-      <c r="BE5" t="n">
+      <c r="BN5" t="n">
         <v>330</v>
       </c>
-      <c r="BF5" t="n">
+      <c r="BO5" t="n">
         <v>330</v>
       </c>
-      <c r="BG5" t="n">
+      <c r="BP5" t="n">
         <v>330</v>
       </c>
-      <c r="BH5" t="n">
+      <c r="BQ5" t="n">
         <v>330</v>
       </c>
-      <c r="BI5" t="n">
+      <c r="BR5" t="n">
         <v>330</v>
       </c>
-      <c r="BJ5" t="n">
+      <c r="BS5" t="n">
         <v>330</v>
       </c>
-      <c r="BK5" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>669</v>
-      </c>
       <c r="BT5" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC5" t="n">
         <v>0.5833333333333334</v>
       </c>
-      <c r="BU5" t="n">
+      <c r="CD5" t="n">
         <v>0.55</v>
       </c>
-      <c r="BV5" t="n">
+      <c r="CE5" t="n">
         <v>0.5333333333333333</v>
       </c>
-      <c r="BW5" t="n">
+      <c r="CF5" t="n">
         <v>0.5263157894736842</v>
       </c>
-      <c r="BX5" t="n">
+      <c r="CG5" t="n">
         <v>0.5106382978723404</v>
       </c>
-      <c r="BY5" t="n">
+      <c r="CH5" t="n">
         <v>0.456140350877193</v>
       </c>
-      <c r="BZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB5" t="n">
+      <c r="CI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK5" t="n">
         <v>0.186046511627907</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>494.12</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>54.63</v>
       </c>
     </row>
     <row r="6">
@@ -1824,10 +2011,10 @@
         <v>501</v>
       </c>
       <c r="C6" t="n">
+        <v>57.82060785767235</v>
+      </c>
+      <c r="D6" t="n">
         <v>39</v>
-      </c>
-      <c r="D6" t="n">
-        <v>57.82060785767235</v>
       </c>
       <c r="E6" t="n">
         <v>501</v>
@@ -1836,720 +2023,819 @@
         <v>200</v>
       </c>
       <c r="G6" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="H6" t="inlineStr">
+        <v>78.5</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I6" t="n">
-        <v>513.7865517018936</v>
-      </c>
-      <c r="J6" t="n">
-        <v>51.04418792941456</v>
-      </c>
-      <c r="K6" t="n">
-        <v>499.5652334048661</v>
-      </c>
-      <c r="L6" t="n">
-        <v>55.33162406055266</v>
-      </c>
-      <c r="M6" t="n">
-        <v>504.0194757976938</v>
-      </c>
-      <c r="N6" t="n">
-        <v>46.73399593568512</v>
-      </c>
-      <c r="O6" t="n">
-        <v>508.4003055587922</v>
-      </c>
-      <c r="P6" t="n">
-        <v>44.65210601729479</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>507.6366781816641</v>
-      </c>
       <c r="R6" t="n">
-        <v>49.50023651144028</v>
+        <v>513.79</v>
       </c>
       <c r="S6" t="n">
-        <v>512.6887774658089</v>
+        <v>51.04</v>
       </c>
       <c r="T6" t="n">
-        <v>47.07742009513419</v>
+        <v>499.57</v>
       </c>
       <c r="U6" t="n">
-        <v>507.8410980456377</v>
+        <v>55.33</v>
       </c>
       <c r="V6" t="n">
-        <v>49.61796654124256</v>
+        <v>504.02</v>
       </c>
       <c r="W6" t="n">
-        <v>511.3628468963057</v>
+        <v>46.73</v>
       </c>
       <c r="X6" t="n">
-        <v>48.48731210566909</v>
+        <v>508.4</v>
       </c>
       <c r="Y6" t="n">
-        <v>509.2222613400215</v>
+        <v>44.65</v>
       </c>
       <c r="Z6" t="n">
-        <v>49.14293266328423</v>
+        <v>507.64</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>49.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>512.6900000000001</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>47.08</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>507.84</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>49.62</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>511.36</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>48.49</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>509.22</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>49.14</v>
       </c>
       <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
         <v>504.6</v>
       </c>
-      <c r="AK6" t="n">
+      <c r="AT6" t="n">
         <v>503.75</v>
       </c>
-      <c r="AL6" t="n">
+      <c r="AU6" t="n">
         <v>503.15</v>
       </c>
-      <c r="AM6" t="n">
+      <c r="AV6" t="n">
         <v>504.43</v>
       </c>
-      <c r="AN6" t="n">
+      <c r="AW6" t="n">
         <v>504.575</v>
       </c>
-      <c r="AO6" t="n">
+      <c r="AX6" t="n">
         <v>504.45</v>
       </c>
-      <c r="AP6" t="n">
+      <c r="AY6" t="n">
         <v>505.11875</v>
       </c>
-      <c r="AQ6" t="n">
+      <c r="AZ6" t="n">
         <v>506.0388888888889</v>
       </c>
-      <c r="AR6" t="n">
+      <c r="BA6" t="n">
         <v>506.625</v>
       </c>
-      <c r="AS6" t="n">
+      <c r="BB6" t="n">
         <v>80.72230175112699</v>
       </c>
-      <c r="AT6" t="n">
+      <c r="BC6" t="n">
         <v>76.09328156940006</v>
       </c>
-      <c r="AU6" t="n">
+      <c r="BD6" t="n">
         <v>72.03351650447172</v>
       </c>
-      <c r="AV6" t="n">
+      <c r="BE6" t="n">
         <v>67.79576019191761</v>
       </c>
-      <c r="AW6" t="n">
+      <c r="BF6" t="n">
         <v>64.44786814420887</v>
       </c>
-      <c r="AX6" t="n">
+      <c r="BG6" t="n">
         <v>62.53448477211823</v>
       </c>
-      <c r="AY6" t="n">
+      <c r="BH6" t="n">
         <v>61.35871697189813</v>
       </c>
-      <c r="AZ6" t="n">
+      <c r="BI6" t="n">
         <v>60.1326648049395</v>
       </c>
-      <c r="BA6" t="n">
+      <c r="BJ6" t="n">
         <v>59.25288495086125</v>
       </c>
-      <c r="BB6" t="n">
+      <c r="BK6" t="n">
         <v>341</v>
       </c>
-      <c r="BC6" t="n">
+      <c r="BL6" t="n">
         <v>341</v>
       </c>
-      <c r="BD6" t="n">
+      <c r="BM6" t="n">
         <v>341</v>
       </c>
-      <c r="BE6" t="n">
+      <c r="BN6" t="n">
         <v>341</v>
       </c>
-      <c r="BF6" t="n">
+      <c r="BO6" t="n">
         <v>341</v>
       </c>
-      <c r="BG6" t="n">
+      <c r="BP6" t="n">
         <v>341</v>
       </c>
-      <c r="BH6" t="n">
+      <c r="BQ6" t="n">
         <v>341</v>
       </c>
-      <c r="BI6" t="n">
+      <c r="BR6" t="n">
         <v>341</v>
       </c>
-      <c r="BJ6" t="n">
+      <c r="BS6" t="n">
         <v>341</v>
       </c>
-      <c r="BK6" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>669</v>
-      </c>
       <c r="BT6" t="n">
-        <v>0</v>
+        <v>669</v>
       </c>
       <c r="BU6" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD6" t="n">
         <v>0.5</v>
       </c>
-      <c r="BV6" t="n">
+      <c r="CE6" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="BW6" t="n">
+      <c r="CF6" t="n">
         <v>0.5</v>
       </c>
-      <c r="BX6" t="n">
+      <c r="CG6" t="n">
         <v>0.5833333333333334</v>
       </c>
-      <c r="BY6" t="n">
+      <c r="CH6" t="n">
         <v>0.5365853658536586</v>
       </c>
-      <c r="BZ6" t="n">
+      <c r="CI6" t="n">
         <v>0.5</v>
       </c>
-      <c r="CA6" t="n">
+      <c r="CJ6" t="n">
         <v>0.5490196078431373</v>
       </c>
-      <c r="CB6" t="n">
+      <c r="CK6" t="n">
         <v>0.5084745762711864</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>509.22</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>49.14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S07_G5_498_40_REL2</t>
+          <t>S06_G5_500_42_REL2</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C7" t="n">
-        <v>40</v>
+        <v>62.26834692364714</v>
       </c>
       <c r="D7" t="n">
-        <v>59.30318754633062</v>
+        <v>42</v>
       </c>
       <c r="E7" t="n">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="F7" t="n">
         <v>200</v>
       </c>
       <c r="G7" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="H7" t="inlineStr">
+        <v>79.5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I7" t="n">
-        <v>487.6102291655517</v>
-      </c>
-      <c r="J7" t="n">
-        <v>49.66478718871344</v>
-      </c>
-      <c r="K7" t="n">
-        <v>493.4353854927505</v>
-      </c>
-      <c r="L7" t="n">
-        <v>44.03143547223276</v>
-      </c>
-      <c r="M7" t="n">
-        <v>491.7237705787329</v>
-      </c>
-      <c r="N7" t="n">
-        <v>36.6260701214927</v>
-      </c>
-      <c r="O7" t="n">
-        <v>499.2182497411656</v>
-      </c>
-      <c r="P7" t="n">
-        <v>38.39319058023241</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>499.6050929660559</v>
-      </c>
       <c r="R7" t="n">
-        <v>38.15750841099072</v>
+        <v>502.6</v>
       </c>
       <c r="S7" t="n">
-        <v>495.6676348272457</v>
+        <v>60.5</v>
       </c>
       <c r="T7" t="n">
-        <v>41.51282505591868</v>
+        <v>490.73</v>
       </c>
       <c r="U7" t="n">
-        <v>498.0776521673081</v>
+        <v>52.15</v>
       </c>
       <c r="V7" t="n">
-        <v>43.98597553788424</v>
+        <v>500.55</v>
       </c>
       <c r="W7" t="n">
-        <v>495.6912322664164</v>
+        <v>51.16</v>
       </c>
       <c r="X7" t="n">
-        <v>48.82993313620857</v>
+        <v>493.6</v>
       </c>
       <c r="Y7" t="n">
-        <v>496.9678894689745</v>
+        <v>49.54</v>
       </c>
       <c r="Z7" t="n">
-        <v>49.79038184818535</v>
+        <v>488.31</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>55.66</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>489.35</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>54.68</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>491.66</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>53.23</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>492.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>56.84</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>495.08</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>54.38</v>
       </c>
       <c r="AJ7" t="n">
-        <v>489.075</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>489.0833333333333</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>490.9625</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>493.07</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>494.3833333333333</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>492.7785714285714</v>
+        <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>492.3875</v>
+        <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>493.1111111111111</v>
+        <v>0</v>
       </c>
       <c r="AR7" t="n">
-        <v>494.715</v>
+        <v>0</v>
       </c>
       <c r="AS7" t="n">
-        <v>84.39561229708568</v>
+        <v>509.15</v>
       </c>
       <c r="AT7" t="n">
-        <v>75.00917536467715</v>
+        <v>506.4166666666667</v>
       </c>
       <c r="AU7" t="n">
-        <v>67.99475048671036</v>
+        <v>504.075</v>
       </c>
       <c r="AV7" t="n">
-        <v>62.97193898872735</v>
+        <v>502.44</v>
       </c>
       <c r="AW7" t="n">
-        <v>59.93526832249012</v>
+        <v>500.3583333333333</v>
       </c>
       <c r="AX7" t="n">
-        <v>58.88961439569348</v>
+        <v>497.5714285714286</v>
       </c>
       <c r="AY7" t="n">
-        <v>59.61144893181175</v>
+        <v>495.5875</v>
       </c>
       <c r="AZ7" t="n">
-        <v>60.7689512176964</v>
+        <v>496.1722222222222</v>
       </c>
       <c r="BA7" t="n">
-        <v>62.28895387626926</v>
+        <v>496.91</v>
       </c>
       <c r="BB7" t="n">
-        <v>319</v>
+        <v>87.96577459444099</v>
       </c>
       <c r="BC7" t="n">
-        <v>319</v>
+        <v>82.04293422078196</v>
       </c>
       <c r="BD7" t="n">
-        <v>319</v>
+        <v>76.16294620745708</v>
       </c>
       <c r="BE7" t="n">
-        <v>319</v>
+        <v>72.10954444454632</v>
       </c>
       <c r="BF7" t="n">
-        <v>319</v>
+        <v>69.20462362122603</v>
       </c>
       <c r="BG7" t="n">
-        <v>319</v>
+        <v>69.23429609017514</v>
       </c>
       <c r="BH7" t="n">
-        <v>319</v>
+        <v>67.81282949228708</v>
       </c>
       <c r="BI7" t="n">
-        <v>319</v>
+        <v>68.43413951104583</v>
       </c>
       <c r="BJ7" t="n">
-        <v>319</v>
+        <v>66.86196153269809</v>
       </c>
       <c r="BK7" t="n">
-        <v>669</v>
+        <v>338</v>
       </c>
       <c r="BL7" t="n">
-        <v>669</v>
+        <v>338</v>
       </c>
       <c r="BM7" t="n">
-        <v>669</v>
+        <v>338</v>
       </c>
       <c r="BN7" t="n">
-        <v>669</v>
+        <v>338</v>
       </c>
       <c r="BO7" t="n">
-        <v>669</v>
+        <v>338</v>
       </c>
       <c r="BP7" t="n">
-        <v>669</v>
+        <v>338</v>
       </c>
       <c r="BQ7" t="n">
-        <v>669</v>
+        <v>338</v>
       </c>
       <c r="BR7" t="n">
-        <v>669</v>
+        <v>338</v>
       </c>
       <c r="BS7" t="n">
-        <v>669</v>
+        <v>338</v>
       </c>
       <c r="BT7" t="n">
-        <v>0</v>
+        <v>669</v>
       </c>
       <c r="BU7" t="n">
-        <v>0</v>
+        <v>669</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.6190476190476191</v>
+        <v>669</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.4333333333333333</v>
+        <v>669</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.5675675675675675</v>
+        <v>669</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.5476190476190477</v>
+        <v>669</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.5348837209302325</v>
+        <v>669</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.5348837209302325</v>
+        <v>669</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.6046511627906976</v>
+        <v>669</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>0.5384615384615384</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>0.6842105263157895</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>0.1052631578947368</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>0.9565217391304348</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>0.9629629629629629</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>0.7941176470588235</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>495.08</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>54.38</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S06_G5_500_42_REL2</t>
+          <t>S07_G5_498_40_REL2</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C8" t="n">
-        <v>42</v>
+        <v>59.30318754633062</v>
       </c>
       <c r="D8" t="n">
-        <v>62.26834692364714</v>
+        <v>40</v>
       </c>
       <c r="E8" t="n">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="F8" t="n">
         <v>200</v>
       </c>
       <c r="G8" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="H8" t="inlineStr">
+        <v>79.5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I8" t="n">
-        <v>502.603484022988</v>
-      </c>
-      <c r="J8" t="n">
-        <v>60.49904823647531</v>
-      </c>
-      <c r="K8" t="n">
-        <v>490.7340862510578</v>
-      </c>
-      <c r="L8" t="n">
-        <v>52.15383174776552</v>
-      </c>
-      <c r="M8" t="n">
-        <v>500.5490977508353</v>
-      </c>
-      <c r="N8" t="n">
-        <v>51.16243924625144</v>
-      </c>
-      <c r="O8" t="n">
-        <v>493.6007970463805</v>
-      </c>
-      <c r="P8" t="n">
-        <v>49.53652235473596</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>488.3135035472203</v>
-      </c>
       <c r="R8" t="n">
-        <v>55.65772751697024</v>
+        <v>487.61</v>
       </c>
       <c r="S8" t="n">
-        <v>489.3460657718541</v>
+        <v>49.66</v>
       </c>
       <c r="T8" t="n">
-        <v>54.68160172029681</v>
+        <v>493.44</v>
       </c>
       <c r="U8" t="n">
-        <v>491.6647936863882</v>
+        <v>44.03</v>
       </c>
       <c r="V8" t="n">
-        <v>53.22751493083302</v>
+        <v>491.72</v>
       </c>
       <c r="W8" t="n">
-        <v>492.4985057828011</v>
+        <v>36.63</v>
       </c>
       <c r="X8" t="n">
-        <v>56.84085360755432</v>
+        <v>499.22</v>
       </c>
       <c r="Y8" t="n">
-        <v>495.0758140090293</v>
+        <v>38.39</v>
       </c>
       <c r="Z8" t="n">
-        <v>54.38065107327292</v>
+        <v>499.61</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>38.16</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>495.67</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>41.51</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>498.08</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>43.99</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>495.69</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>48.83</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>496.97</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>49.79</v>
       </c>
       <c r="AJ8" t="n">
-        <v>509.15</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>506.4166666666667</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>504.075</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>502.44</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>500.3583333333333</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>497.5714285714286</v>
+        <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>495.5875</v>
+        <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>496.1722222222222</v>
+        <v>0</v>
       </c>
       <c r="AR8" t="n">
-        <v>496.91</v>
+        <v>0</v>
       </c>
       <c r="AS8" t="n">
-        <v>87.96577459444099</v>
+        <v>489.075</v>
       </c>
       <c r="AT8" t="n">
-        <v>82.04293422078196</v>
+        <v>489.0833333333333</v>
       </c>
       <c r="AU8" t="n">
-        <v>76.16294620745708</v>
+        <v>490.9625</v>
       </c>
       <c r="AV8" t="n">
-        <v>72.10954444454632</v>
+        <v>493.07</v>
       </c>
       <c r="AW8" t="n">
-        <v>69.20462362122603</v>
+        <v>494.3833333333333</v>
       </c>
       <c r="AX8" t="n">
-        <v>69.23429609017514</v>
+        <v>492.7785714285714</v>
       </c>
       <c r="AY8" t="n">
-        <v>67.81282949228708</v>
+        <v>492.3875</v>
       </c>
       <c r="AZ8" t="n">
-        <v>68.43413951104583</v>
+        <v>493.1111111111111</v>
       </c>
       <c r="BA8" t="n">
-        <v>66.86196153269809</v>
+        <v>494.715</v>
       </c>
       <c r="BB8" t="n">
-        <v>338</v>
+        <v>84.39561229708568</v>
       </c>
       <c r="BC8" t="n">
-        <v>338</v>
+        <v>75.00917536467715</v>
       </c>
       <c r="BD8" t="n">
-        <v>338</v>
+        <v>67.99475048671036</v>
       </c>
       <c r="BE8" t="n">
-        <v>338</v>
+        <v>62.97193898872735</v>
       </c>
       <c r="BF8" t="n">
-        <v>338</v>
+        <v>59.93526832249012</v>
       </c>
       <c r="BG8" t="n">
-        <v>338</v>
+        <v>58.88961439569348</v>
       </c>
       <c r="BH8" t="n">
-        <v>338</v>
+        <v>59.61144893181175</v>
       </c>
       <c r="BI8" t="n">
-        <v>338</v>
+        <v>60.7689512176964</v>
       </c>
       <c r="BJ8" t="n">
-        <v>338</v>
+        <v>62.28895387626926</v>
       </c>
       <c r="BK8" t="n">
-        <v>669</v>
+        <v>319</v>
       </c>
       <c r="BL8" t="n">
-        <v>669</v>
+        <v>319</v>
       </c>
       <c r="BM8" t="n">
-        <v>669</v>
+        <v>319</v>
       </c>
       <c r="BN8" t="n">
-        <v>669</v>
+        <v>319</v>
       </c>
       <c r="BO8" t="n">
-        <v>669</v>
+        <v>319</v>
       </c>
       <c r="BP8" t="n">
-        <v>669</v>
+        <v>319</v>
       </c>
       <c r="BQ8" t="n">
-        <v>669</v>
+        <v>319</v>
       </c>
       <c r="BR8" t="n">
-        <v>669</v>
+        <v>319</v>
       </c>
       <c r="BS8" t="n">
-        <v>669</v>
+        <v>319</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.5384615384615384</v>
+        <v>669</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.6842105263157895</v>
+        <v>669</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.1052631578947368</v>
+        <v>669</v>
       </c>
       <c r="BW8" t="n">
-        <v>1</v>
+        <v>669</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.9565217391304348</v>
+        <v>669</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.9629629629629629</v>
+        <v>669</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.9</v>
+        <v>669</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.7941176470588235</v>
+        <v>669</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.8</v>
+        <v>669</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>0.6190476190476191</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>0.4333333333333333</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>0.5675675675675675</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>0.5476190476190477</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>0.5348837209302325</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>0.5348837209302325</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>0.6046511627906976</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>496.97</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>49.79</v>
       </c>
     </row>
     <row r="9">
@@ -2562,10 +2848,10 @@
         <v>499</v>
       </c>
       <c r="C9" t="n">
+        <v>56.33802816901409</v>
+      </c>
+      <c r="D9" t="n">
         <v>38</v>
-      </c>
-      <c r="D9" t="n">
-        <v>56.33802816901409</v>
       </c>
       <c r="E9" t="n">
         <v>499</v>
@@ -2574,228 +2860,261 @@
         <v>200</v>
       </c>
       <c r="G9" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="H9" t="inlineStr">
+        <v>82</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I9" t="n">
-        <v>501.0864732841286</v>
-      </c>
-      <c r="J9" t="n">
-        <v>40.6834849925042</v>
-      </c>
-      <c r="K9" t="n">
-        <v>503.6835948220291</v>
-      </c>
-      <c r="L9" t="n">
-        <v>38.20557294772453</v>
-      </c>
-      <c r="M9" t="n">
-        <v>500.0621354105143</v>
-      </c>
-      <c r="N9" t="n">
-        <v>35.35740279586806</v>
-      </c>
-      <c r="O9" t="n">
-        <v>497.6270839677031</v>
-      </c>
-      <c r="P9" t="n">
-        <v>37.04660765096991</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>488.3708523605108</v>
-      </c>
       <c r="R9" t="n">
-        <v>41.21375403405757</v>
+        <v>501.09</v>
       </c>
       <c r="S9" t="n">
-        <v>490.452011895739</v>
+        <v>40.68</v>
       </c>
       <c r="T9" t="n">
-        <v>37.85623340394145</v>
+        <v>503.68</v>
       </c>
       <c r="U9" t="n">
-        <v>491.1343475949722</v>
+        <v>38.21</v>
       </c>
       <c r="V9" t="n">
-        <v>37.98210553883305</v>
+        <v>500.06</v>
       </c>
       <c r="W9" t="n">
-        <v>491.8113036023225</v>
+        <v>35.36</v>
       </c>
       <c r="X9" t="n">
-        <v>38.17833541874747</v>
+        <v>497.63</v>
       </c>
       <c r="Y9" t="n">
-        <v>490.8313373587263</v>
+        <v>37.05</v>
       </c>
       <c r="Z9" t="n">
-        <v>38.36661703821588</v>
+        <v>488.37</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>41.21</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>490.45</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>37.86</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>491.13</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>37.98</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>491.81</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>38.18</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>490.83</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>38.37</v>
       </c>
       <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
         <v>501.375</v>
       </c>
-      <c r="AK9" t="n">
+      <c r="AT9" t="n">
         <v>499.2833333333334</v>
       </c>
-      <c r="AL9" t="n">
+      <c r="AU9" t="n">
         <v>499.9875</v>
       </c>
-      <c r="AM9" t="n">
+      <c r="AV9" t="n">
         <v>499.93</v>
       </c>
-      <c r="AN9" t="n">
+      <c r="AW9" t="n">
         <v>499.7083333333333</v>
       </c>
-      <c r="AO9" t="n">
+      <c r="AX9" t="n">
         <v>498.4214285714286</v>
       </c>
-      <c r="AP9" t="n">
+      <c r="AY9" t="n">
         <v>497.975</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AZ9" t="n">
         <v>497.7055555555556</v>
       </c>
-      <c r="AR9" t="n">
+      <c r="BA9" t="n">
         <v>497.125</v>
       </c>
-      <c r="AS9" t="n">
+      <c r="BB9" t="n">
         <v>86.0832990480732</v>
       </c>
-      <c r="AT9" t="n">
+      <c r="BC9" t="n">
         <v>75.90785898413652</v>
       </c>
-      <c r="AU9" t="n">
+      <c r="BD9" t="n">
         <v>68.60475452729206</v>
       </c>
-      <c r="AV9" t="n">
+      <c r="BE9" t="n">
         <v>64.04939578169336</v>
       </c>
-      <c r="AW9" t="n">
+      <c r="BF9" t="n">
         <v>61.04525586717521</v>
       </c>
-      <c r="AX9" t="n">
+      <c r="BG9" t="n">
         <v>59.49490588723216</v>
       </c>
-      <c r="AY9" t="n">
+      <c r="BH9" t="n">
         <v>57.73061904223788</v>
       </c>
-      <c r="AZ9" t="n">
+      <c r="BI9" t="n">
         <v>56.19061776392353</v>
       </c>
-      <c r="BA9" t="n">
+      <c r="BJ9" t="n">
         <v>54.78612392750559</v>
       </c>
-      <c r="BB9" t="n">
+      <c r="BK9" t="n">
         <v>317</v>
       </c>
-      <c r="BC9" t="n">
+      <c r="BL9" t="n">
         <v>317</v>
       </c>
-      <c r="BD9" t="n">
+      <c r="BM9" t="n">
         <v>317</v>
       </c>
-      <c r="BE9" t="n">
+      <c r="BN9" t="n">
         <v>317</v>
       </c>
-      <c r="BF9" t="n">
+      <c r="BO9" t="n">
         <v>317</v>
       </c>
-      <c r="BG9" t="n">
+      <c r="BP9" t="n">
         <v>317</v>
       </c>
-      <c r="BH9" t="n">
+      <c r="BQ9" t="n">
         <v>317</v>
       </c>
-      <c r="BI9" t="n">
+      <c r="BR9" t="n">
         <v>317</v>
       </c>
-      <c r="BJ9" t="n">
+      <c r="BS9" t="n">
         <v>317</v>
       </c>
-      <c r="BK9" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>669</v>
-      </c>
       <c r="BT9" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC9" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="BU9" t="n">
+      <c r="CD9" t="n">
         <v>0.8181818181818182</v>
       </c>
-      <c r="BV9" t="n">
+      <c r="CE9" t="n">
         <v>0.7777777777777778</v>
       </c>
-      <c r="BW9" t="n">
+      <c r="CF9" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="BX9" t="n">
+      <c r="CG9" t="n">
         <v>0.6052631578947368</v>
       </c>
-      <c r="BY9" t="n">
+      <c r="CH9" t="n">
         <v>0.625</v>
       </c>
-      <c r="BZ9" t="n">
+      <c r="CI9" t="n">
         <v>0.6206896551724138</v>
       </c>
-      <c r="CA9" t="n">
+      <c r="CJ9" t="n">
         <v>0.5735294117647058</v>
       </c>
-      <c r="CB9" t="n">
+      <c r="CK9" t="n">
         <v>0.6133333333333333</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>490.83</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>38.37</v>
       </c>
     </row>
     <row r="10">
@@ -2808,10 +3127,10 @@
         <v>502</v>
       </c>
       <c r="C10" t="n">
+        <v>62.26834692364714</v>
+      </c>
+      <c r="D10" t="n">
         <v>42</v>
-      </c>
-      <c r="D10" t="n">
-        <v>62.26834692364714</v>
       </c>
       <c r="E10" t="n">
         <v>502</v>
@@ -2820,228 +3139,261 @@
         <v>200</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H10" t="inlineStr">
+        <v>78</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I10" t="n">
-        <v>480.6086585943544</v>
-      </c>
-      <c r="J10" t="n">
-        <v>51.75971968126237</v>
-      </c>
-      <c r="K10" t="n">
-        <v>483.9486803853009</v>
-      </c>
-      <c r="L10" t="n">
-        <v>55.39988233094481</v>
-      </c>
-      <c r="M10" t="n">
-        <v>485.4745813570726</v>
-      </c>
-      <c r="N10" t="n">
-        <v>56.28086187622174</v>
-      </c>
-      <c r="O10" t="n">
-        <v>486.0151363862694</v>
-      </c>
-      <c r="P10" t="n">
-        <v>51.54785835407029</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>496.4932156432854</v>
-      </c>
       <c r="R10" t="n">
-        <v>57.52128124176838</v>
+        <v>480.61</v>
       </c>
       <c r="S10" t="n">
-        <v>493.2139439727952</v>
+        <v>51.76</v>
       </c>
       <c r="T10" t="n">
-        <v>55.19352294829414</v>
+        <v>483.95</v>
       </c>
       <c r="U10" t="n">
-        <v>495.7468291167348</v>
+        <v>55.4</v>
       </c>
       <c r="V10" t="n">
-        <v>54.13935272781854</v>
+        <v>485.47</v>
       </c>
       <c r="W10" t="n">
-        <v>492.3713596964054</v>
+        <v>56.28</v>
       </c>
       <c r="X10" t="n">
-        <v>55.67229315924841</v>
+        <v>486.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>495.5434474155448</v>
+        <v>51.55</v>
       </c>
       <c r="Z10" t="n">
-        <v>55.62355676546776</v>
+        <v>496.49</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>57.52</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>493.21</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>55.19</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>495.75</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>54.14</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>492.37</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>55.67</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>495.54</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>55.62</v>
       </c>
       <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
         <v>498.15</v>
       </c>
-      <c r="AK10" t="n">
+      <c r="AT10" t="n">
         <v>495.0166666666667</v>
       </c>
-      <c r="AL10" t="n">
+      <c r="AU10" t="n">
         <v>493.55</v>
       </c>
-      <c r="AM10" t="n">
+      <c r="AV10" t="n">
         <v>492.41</v>
       </c>
-      <c r="AN10" t="n">
+      <c r="AW10" t="n">
         <v>493.85</v>
       </c>
-      <c r="AO10" t="n">
+      <c r="AX10" t="n">
         <v>494.4357142857143</v>
       </c>
-      <c r="AP10" t="n">
+      <c r="AY10" t="n">
         <v>494.8375</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AZ10" t="n">
         <v>494.4944444444445</v>
       </c>
-      <c r="AR10" t="n">
+      <c r="BA10" t="n">
         <v>494.775</v>
       </c>
-      <c r="AS10" t="n">
+      <c r="BB10" t="n">
         <v>86.92713903033965</v>
       </c>
-      <c r="AT10" t="n">
+      <c r="BC10" t="n">
         <v>80.91384135129306</v>
       </c>
-      <c r="AU10" t="n">
+      <c r="BD10" t="n">
         <v>77.20733449614744</v>
       </c>
-      <c r="AV10" t="n">
+      <c r="BE10" t="n">
         <v>73.44482214560806</v>
       </c>
-      <c r="AW10" t="n">
+      <c r="BF10" t="n">
         <v>69.28607965048487</v>
       </c>
-      <c r="AX10" t="n">
+      <c r="BG10" t="n">
         <v>67.61521497354251</v>
       </c>
-      <c r="AY10" t="n">
+      <c r="BH10" t="n">
         <v>65.7341128619684</v>
       </c>
-      <c r="AZ10" t="n">
+      <c r="BI10" t="n">
         <v>64.83264757325605</v>
       </c>
-      <c r="BA10" t="n">
+      <c r="BJ10" t="n">
         <v>64.34348743268428</v>
       </c>
-      <c r="BB10" t="n">
+      <c r="BK10" t="n">
         <v>322</v>
       </c>
-      <c r="BC10" t="n">
+      <c r="BL10" t="n">
         <v>322</v>
       </c>
-      <c r="BD10" t="n">
+      <c r="BM10" t="n">
         <v>322</v>
       </c>
-      <c r="BE10" t="n">
+      <c r="BN10" t="n">
         <v>322</v>
       </c>
-      <c r="BF10" t="n">
+      <c r="BO10" t="n">
         <v>322</v>
       </c>
-      <c r="BG10" t="n">
+      <c r="BP10" t="n">
         <v>322</v>
       </c>
-      <c r="BH10" t="n">
+      <c r="BQ10" t="n">
         <v>322</v>
       </c>
-      <c r="BI10" t="n">
+      <c r="BR10" t="n">
         <v>322</v>
       </c>
-      <c r="BJ10" t="n">
+      <c r="BS10" t="n">
         <v>322</v>
       </c>
-      <c r="BK10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>669</v>
-      </c>
       <c r="BT10" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC10" t="n">
         <v>0.875</v>
       </c>
-      <c r="BU10" t="n">
+      <c r="CD10" t="n">
         <v>0.8666666666666667</v>
       </c>
-      <c r="BV10" t="n">
+      <c r="CE10" t="n">
         <v>0.72</v>
       </c>
-      <c r="BW10" t="n">
+      <c r="CF10" t="n">
         <v>0.8076923076923077</v>
       </c>
-      <c r="BX10" t="n">
+      <c r="CG10" t="n">
         <v>0.8076923076923077</v>
       </c>
-      <c r="BY10" t="n">
+      <c r="CH10" t="n">
         <v>0.6363636363636364</v>
       </c>
-      <c r="BZ10" t="n">
+      <c r="CI10" t="n">
         <v>0.6470588235294118</v>
       </c>
-      <c r="CA10" t="n">
+      <c r="CJ10" t="n">
         <v>0.631578947368421</v>
       </c>
-      <c r="CB10" t="n">
+      <c r="CK10" t="n">
         <v>0.6666666666666666</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>495.54</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>55.62</v>
       </c>
     </row>
     <row r="11">
@@ -3054,10 +3406,10 @@
         <v>498</v>
       </c>
       <c r="C11" t="n">
+        <v>62.26834692364714</v>
+      </c>
+      <c r="D11" t="n">
         <v>42</v>
-      </c>
-      <c r="D11" t="n">
-        <v>62.26834692364714</v>
       </c>
       <c r="E11" t="n">
         <v>498</v>
@@ -3066,228 +3418,261 @@
         <v>200</v>
       </c>
       <c r="G11" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="H11" t="inlineStr">
+        <v>80.5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I11" t="n">
-        <v>442.5214387168094</v>
-      </c>
-      <c r="J11" t="n">
-        <v>48.34728932915898</v>
-      </c>
-      <c r="K11" t="n">
-        <v>477.1048626559821</v>
-      </c>
-      <c r="L11" t="n">
-        <v>58.49607332695079</v>
-      </c>
-      <c r="M11" t="n">
-        <v>473.0163337743059</v>
-      </c>
-      <c r="N11" t="n">
-        <v>48.66788897433559</v>
-      </c>
-      <c r="O11" t="n">
-        <v>477.235399127604</v>
-      </c>
-      <c r="P11" t="n">
-        <v>50.1740815378142</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>482.2748826274653</v>
-      </c>
       <c r="R11" t="n">
-        <v>49.78414411167068</v>
+        <v>442.52</v>
       </c>
       <c r="S11" t="n">
-        <v>481.6439044958827</v>
+        <v>48.35</v>
       </c>
       <c r="T11" t="n">
-        <v>45.93288700081056</v>
+        <v>477.1</v>
       </c>
       <c r="U11" t="n">
-        <v>486.4421263545435</v>
+        <v>58.5</v>
       </c>
       <c r="V11" t="n">
-        <v>45.22733040096366</v>
+        <v>473.02</v>
       </c>
       <c r="W11" t="n">
-        <v>491.3025959820401</v>
+        <v>48.67</v>
       </c>
       <c r="X11" t="n">
-        <v>48.6331732507284</v>
+        <v>477.24</v>
       </c>
       <c r="Y11" t="n">
-        <v>493.3486133462285</v>
+        <v>50.17</v>
       </c>
       <c r="Z11" t="n">
-        <v>47.03897804303187</v>
+        <v>482.27</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>49.78</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>481.64</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>45.93</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>486.44</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>45.23</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>491.3</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>48.63</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>493.35</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>47.04</v>
       </c>
       <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
         <v>470.9</v>
       </c>
-      <c r="AK11" t="n">
+      <c r="AT11" t="n">
         <v>468.55</v>
       </c>
-      <c r="AL11" t="n">
+      <c r="AU11" t="n">
         <v>470.3625</v>
       </c>
-      <c r="AM11" t="n">
+      <c r="AV11" t="n">
         <v>471.94</v>
       </c>
-      <c r="AN11" t="n">
+      <c r="AW11" t="n">
         <v>475.3666666666667</v>
       </c>
-      <c r="AO11" t="n">
+      <c r="AX11" t="n">
         <v>478.8428571428572</v>
       </c>
-      <c r="AP11" t="n">
+      <c r="AY11" t="n">
         <v>481.36875</v>
       </c>
-      <c r="AQ11" t="n">
+      <c r="AZ11" t="n">
         <v>483.8555555555556</v>
       </c>
-      <c r="AR11" t="n">
+      <c r="BA11" t="n">
         <v>487.18</v>
       </c>
-      <c r="AS11" t="n">
+      <c r="BB11" t="n">
         <v>87.01172334806385</v>
       </c>
-      <c r="AT11" t="n">
+      <c r="BC11" t="n">
         <v>80.81840240110334</v>
       </c>
-      <c r="AU11" t="n">
+      <c r="BD11" t="n">
         <v>75.84033289582793</v>
       </c>
-      <c r="AV11" t="n">
+      <c r="BE11" t="n">
         <v>71.39605311219941</v>
       </c>
-      <c r="AW11" t="n">
+      <c r="BF11" t="n">
         <v>70.04283609969609</v>
       </c>
-      <c r="AX11" t="n">
+      <c r="BG11" t="n">
         <v>68.04360696626533</v>
       </c>
-      <c r="AY11" t="n">
+      <c r="BH11" t="n">
         <v>65.14537798982748</v>
       </c>
-      <c r="AZ11" t="n">
+      <c r="BI11" t="n">
         <v>63.46968849793333</v>
       </c>
-      <c r="BA11" t="n">
+      <c r="BJ11" t="n">
         <v>63.14861518671648</v>
       </c>
-      <c r="BB11" t="n">
+      <c r="BK11" t="n">
         <v>321</v>
       </c>
-      <c r="BC11" t="n">
+      <c r="BL11" t="n">
         <v>321</v>
       </c>
-      <c r="BD11" t="n">
+      <c r="BM11" t="n">
         <v>321</v>
       </c>
-      <c r="BE11" t="n">
+      <c r="BN11" t="n">
         <v>321</v>
       </c>
-      <c r="BF11" t="n">
+      <c r="BO11" t="n">
         <v>321</v>
       </c>
-      <c r="BG11" t="n">
+      <c r="BP11" t="n">
         <v>321</v>
       </c>
-      <c r="BH11" t="n">
+      <c r="BQ11" t="n">
         <v>321</v>
       </c>
-      <c r="BI11" t="n">
+      <c r="BR11" t="n">
         <v>321</v>
       </c>
-      <c r="BJ11" t="n">
+      <c r="BS11" t="n">
         <v>321</v>
       </c>
-      <c r="BK11" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>669</v>
-      </c>
       <c r="BT11" t="n">
-        <v>0</v>
+        <v>669</v>
       </c>
       <c r="BU11" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB11" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD11" t="n">
         <v>0.6875</v>
       </c>
-      <c r="BV11" t="n">
+      <c r="CE11" t="n">
         <v>0.7894736842105263</v>
       </c>
-      <c r="BW11" t="n">
+      <c r="CF11" t="n">
         <v>0.6785714285714286</v>
       </c>
-      <c r="BX11" t="n">
+      <c r="CG11" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="BY11" t="n">
+      <c r="CH11" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="BZ11" t="n">
+      <c r="CI11" t="n">
         <v>0.6451612903225806</v>
       </c>
-      <c r="CA11" t="n">
+      <c r="CJ11" t="n">
         <v>0.5555555555555556</v>
       </c>
-      <c r="CB11" t="n">
+      <c r="CK11" t="n">
         <v>0.5555555555555556</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>493.35</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>47.04</v>
       </c>
     </row>
     <row r="12">
@@ -3300,10 +3685,10 @@
         <v>498</v>
       </c>
       <c r="C12" t="n">
+        <v>59.30318754633062</v>
+      </c>
+      <c r="D12" t="n">
         <v>40</v>
-      </c>
-      <c r="D12" t="n">
-        <v>59.30318754633062</v>
       </c>
       <c r="E12" t="n">
         <v>498</v>
@@ -3312,228 +3697,261 @@
         <v>200</v>
       </c>
       <c r="G12" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="H12" t="inlineStr">
+        <v>80.5</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I12" t="n">
-        <v>509.7878652332254</v>
-      </c>
-      <c r="J12" t="n">
-        <v>45.89850836391813</v>
-      </c>
-      <c r="K12" t="n">
-        <v>512.732891424405</v>
-      </c>
-      <c r="L12" t="n">
-        <v>49.82660589798889</v>
-      </c>
-      <c r="M12" t="n">
-        <v>510.9006537721765</v>
-      </c>
-      <c r="N12" t="n">
-        <v>44.46734639444068</v>
-      </c>
-      <c r="O12" t="n">
-        <v>507.2289050402225</v>
-      </c>
-      <c r="P12" t="n">
-        <v>42.73889694166633</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>502.9499792663967</v>
-      </c>
       <c r="R12" t="n">
-        <v>45.53498024180546</v>
+        <v>509.79</v>
       </c>
       <c r="S12" t="n">
-        <v>503.5503368640989</v>
+        <v>45.9</v>
       </c>
       <c r="T12" t="n">
-        <v>50.94418999247448</v>
+        <v>512.73</v>
       </c>
       <c r="U12" t="n">
-        <v>500.7300948955527</v>
+        <v>49.83</v>
       </c>
       <c r="V12" t="n">
-        <v>47.74833677966761</v>
+        <v>510.9</v>
       </c>
       <c r="W12" t="n">
-        <v>497.736819309876</v>
+        <v>44.47</v>
       </c>
       <c r="X12" t="n">
-        <v>45.41388221602119</v>
+        <v>507.23</v>
       </c>
       <c r="Y12" t="n">
-        <v>492.9916150352441</v>
+        <v>42.74</v>
       </c>
       <c r="Z12" t="n">
-        <v>45.62105313392064</v>
+        <v>502.95</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>45.53</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>503.55</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>50.94</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>500.73</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>47.75</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>497.74</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>45.41</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>492.99</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>45.62</v>
       </c>
       <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
         <v>501.725</v>
       </c>
-      <c r="AK12" t="n">
+      <c r="AT12" t="n">
         <v>503.05</v>
       </c>
-      <c r="AL12" t="n">
+      <c r="AU12" t="n">
         <v>503.65</v>
       </c>
-      <c r="AM12" t="n">
+      <c r="AV12" t="n">
         <v>503.99</v>
       </c>
-      <c r="AN12" t="n">
+      <c r="AW12" t="n">
         <v>504.3916666666667</v>
       </c>
-      <c r="AO12" t="n">
+      <c r="AX12" t="n">
         <v>504.7642857142857</v>
       </c>
-      <c r="AP12" t="n">
+      <c r="AY12" t="n">
         <v>504.725</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AZ12" t="n">
         <v>503.9166666666667</v>
       </c>
-      <c r="AR12" t="n">
+      <c r="BA12" t="n">
         <v>503.67</v>
       </c>
-      <c r="AS12" t="n">
+      <c r="BB12" t="n">
         <v>77.07106704204892</v>
       </c>
-      <c r="AT12" t="n">
+      <c r="BC12" t="n">
         <v>70.29400756821309</v>
       </c>
-      <c r="AU12" t="n">
+      <c r="BD12" t="n">
         <v>66.73475481336543</v>
       </c>
-      <c r="AV12" t="n">
+      <c r="BE12" t="n">
         <v>63.88873061816144</v>
       </c>
-      <c r="AW12" t="n">
+      <c r="BF12" t="n">
         <v>61.66067031657123</v>
       </c>
-      <c r="AX12" t="n">
+      <c r="BG12" t="n">
         <v>60.20828261890857</v>
       </c>
-      <c r="AY12" t="n">
+      <c r="BH12" t="n">
         <v>58.89757528965009</v>
       </c>
-      <c r="AZ12" t="n">
+      <c r="BI12" t="n">
         <v>57.3147135462517</v>
       </c>
-      <c r="BA12" t="n">
+      <c r="BJ12" t="n">
         <v>56.9313718436505</v>
       </c>
-      <c r="BB12" t="n">
+      <c r="BK12" t="n">
         <v>333</v>
       </c>
-      <c r="BC12" t="n">
+      <c r="BL12" t="n">
         <v>333</v>
       </c>
-      <c r="BD12" t="n">
+      <c r="BM12" t="n">
         <v>333</v>
       </c>
-      <c r="BE12" t="n">
+      <c r="BN12" t="n">
         <v>333</v>
       </c>
-      <c r="BF12" t="n">
+      <c r="BO12" t="n">
         <v>333</v>
       </c>
-      <c r="BG12" t="n">
+      <c r="BP12" t="n">
         <v>333</v>
       </c>
-      <c r="BH12" t="n">
+      <c r="BQ12" t="n">
         <v>333</v>
       </c>
-      <c r="BI12" t="n">
+      <c r="BR12" t="n">
         <v>333</v>
       </c>
-      <c r="BJ12" t="n">
+      <c r="BS12" t="n">
         <v>333</v>
       </c>
-      <c r="BK12" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>669</v>
-      </c>
       <c r="BT12" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC12" t="n">
         <v>0.75</v>
       </c>
-      <c r="BU12" t="n">
+      <c r="CD12" t="n">
         <v>0.6818181818181818</v>
       </c>
-      <c r="BV12" t="n">
+      <c r="CE12" t="n">
         <v>0.625</v>
       </c>
-      <c r="BW12" t="n">
+      <c r="CF12" t="n">
         <v>0.5476190476190477</v>
       </c>
-      <c r="BX12" t="n">
+      <c r="CG12" t="n">
         <v>0.5</v>
       </c>
-      <c r="BY12" t="n">
+      <c r="CH12" t="n">
         <v>0.5</v>
       </c>
-      <c r="BZ12" t="n">
+      <c r="CI12" t="n">
         <v>0.5652173913043478</v>
       </c>
-      <c r="CA12" t="n">
+      <c r="CJ12" t="n">
         <v>0.6956521739130435</v>
       </c>
-      <c r="CB12" t="n">
+      <c r="CK12" t="n">
         <v>0.7971014492753623</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>492.99</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>45.62</v>
       </c>
     </row>
     <row r="13">
@@ -3546,10 +3964,10 @@
         <v>501</v>
       </c>
       <c r="C13" t="n">
+        <v>59.30318754633062</v>
+      </c>
+      <c r="D13" t="n">
         <v>40</v>
-      </c>
-      <c r="D13" t="n">
-        <v>59.30318754633062</v>
       </c>
       <c r="E13" t="n">
         <v>501</v>
@@ -3558,228 +3976,261 @@
         <v>200</v>
       </c>
       <c r="G13" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="H13" t="inlineStr">
+        <v>79.5</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Q13" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I13" t="n">
-        <v>473.2673897102472</v>
-      </c>
-      <c r="J13" t="n">
-        <v>32.59904825103816</v>
-      </c>
-      <c r="K13" t="n">
-        <v>482.0068468528319</v>
-      </c>
-      <c r="L13" t="n">
-        <v>40.27291008642542</v>
-      </c>
-      <c r="M13" t="n">
-        <v>486.4972375281637</v>
-      </c>
-      <c r="N13" t="n">
-        <v>45.50704838703379</v>
-      </c>
-      <c r="O13" t="n">
-        <v>490.462641101152</v>
-      </c>
-      <c r="P13" t="n">
-        <v>47.60409989015457</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>495.5489989275706</v>
-      </c>
       <c r="R13" t="n">
-        <v>47.30406426832187</v>
+        <v>473.27</v>
       </c>
       <c r="S13" t="n">
-        <v>494.0301667709512</v>
+        <v>32.6</v>
       </c>
       <c r="T13" t="n">
-        <v>48.21944990479243</v>
+        <v>482.01</v>
       </c>
       <c r="U13" t="n">
-        <v>496.5324866637019</v>
+        <v>40.27</v>
       </c>
       <c r="V13" t="n">
-        <v>49.57472851732648</v>
+        <v>486.5</v>
       </c>
       <c r="W13" t="n">
-        <v>498.5424990171535</v>
+        <v>45.51</v>
       </c>
       <c r="X13" t="n">
-        <v>50.25863447297777</v>
+        <v>490.46</v>
       </c>
       <c r="Y13" t="n">
-        <v>499.9710858765816</v>
+        <v>47.6</v>
       </c>
       <c r="Z13" t="n">
-        <v>48.71485913692668</v>
+        <v>495.55</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>47.3</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>494.03</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>48.22</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>496.53</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>49.57</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>498.54</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>50.26</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>499.97</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>48.71</v>
       </c>
       <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
         <v>492.125</v>
       </c>
-      <c r="AK13" t="n">
+      <c r="AT13" t="n">
         <v>485.4666666666666</v>
       </c>
-      <c r="AL13" t="n">
+      <c r="AU13" t="n">
         <v>485.6125</v>
       </c>
-      <c r="AM13" t="n">
+      <c r="AV13" t="n">
         <v>487.07</v>
       </c>
-      <c r="AN13" t="n">
+      <c r="AW13" t="n">
         <v>490.65</v>
       </c>
-      <c r="AO13" t="n">
+      <c r="AX13" t="n">
         <v>493.1357142857143</v>
       </c>
-      <c r="AP13" t="n">
+      <c r="AY13" t="n">
         <v>496.025</v>
       </c>
-      <c r="AQ13" t="n">
+      <c r="AZ13" t="n">
         <v>497.9277777777778</v>
       </c>
-      <c r="AR13" t="n">
+      <c r="BA13" t="n">
         <v>499.765</v>
       </c>
-      <c r="AS13" t="n">
+      <c r="BB13" t="n">
         <v>78.80266096395476</v>
       </c>
-      <c r="AT13" t="n">
+      <c r="BC13" t="n">
         <v>69.45225378312468</v>
       </c>
-      <c r="AU13" t="n">
+      <c r="BD13" t="n">
         <v>65.61449796919885</v>
       </c>
-      <c r="AV13" t="n">
+      <c r="BE13" t="n">
         <v>63.04859316432049</v>
       </c>
-      <c r="AW13" t="n">
+      <c r="BF13" t="n">
         <v>62.29347879192493</v>
       </c>
-      <c r="AX13" t="n">
+      <c r="BG13" t="n">
         <v>61.13757445470078</v>
       </c>
-      <c r="AY13" t="n">
+      <c r="BH13" t="n">
         <v>62.10494646161447</v>
       </c>
-      <c r="AZ13" t="n">
+      <c r="BI13" t="n">
         <v>61.11846698153382</v>
       </c>
-      <c r="BA13" t="n">
+      <c r="BJ13" t="n">
         <v>62.1197213049125</v>
       </c>
-      <c r="BB13" t="n">
+      <c r="BK13" t="n">
         <v>333</v>
       </c>
-      <c r="BC13" t="n">
+      <c r="BL13" t="n">
         <v>333</v>
       </c>
-      <c r="BD13" t="n">
+      <c r="BM13" t="n">
         <v>333</v>
       </c>
-      <c r="BE13" t="n">
+      <c r="BN13" t="n">
         <v>333</v>
       </c>
-      <c r="BF13" t="n">
+      <c r="BO13" t="n">
         <v>333</v>
       </c>
-      <c r="BG13" t="n">
+      <c r="BP13" t="n">
         <v>333</v>
       </c>
-      <c r="BH13" t="n">
+      <c r="BQ13" t="n">
         <v>333</v>
       </c>
-      <c r="BI13" t="n">
+      <c r="BR13" t="n">
         <v>333</v>
       </c>
-      <c r="BJ13" t="n">
+      <c r="BS13" t="n">
         <v>333</v>
       </c>
-      <c r="BK13" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>669</v>
-      </c>
       <c r="BT13" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB13" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC13" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="BU13" t="n">
+      <c r="CD13" t="n">
         <v>0.8181818181818182</v>
       </c>
-      <c r="BV13" t="n">
+      <c r="CE13" t="n">
         <v>0.75</v>
       </c>
-      <c r="BW13" t="n">
+      <c r="CF13" t="n">
         <v>0.9565217391304348</v>
       </c>
-      <c r="BX13" t="n">
+      <c r="CG13" t="n">
         <v>0.92</v>
       </c>
-      <c r="BY13" t="n">
+      <c r="CH13" t="n">
         <v>0.8846153846153846</v>
       </c>
-      <c r="BZ13" t="n">
+      <c r="CI13" t="n">
         <v>0.8518518518518519</v>
       </c>
-      <c r="CA13" t="n">
+      <c r="CJ13" t="n">
         <v>0.8518518518518519</v>
       </c>
-      <c r="CB13" t="n">
+      <c r="CK13" t="n">
         <v>0.7931034482758621</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>499.97</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>48.71</v>
       </c>
     </row>
     <row r="14">
@@ -3792,10 +4243,10 @@
         <v>502</v>
       </c>
       <c r="C14" t="n">
+        <v>60.78576723498888</v>
+      </c>
+      <c r="D14" t="n">
         <v>41</v>
-      </c>
-      <c r="D14" t="n">
-        <v>60.78576723498888</v>
       </c>
       <c r="E14" t="n">
         <v>502</v>
@@ -3804,228 +4255,261 @@
         <v>200</v>
       </c>
       <c r="G14" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="H14" t="inlineStr">
+        <v>79.5</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Q14" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I14" t="n">
-        <v>473.8747468572994</v>
-      </c>
-      <c r="J14" t="n">
-        <v>47.57863143792608</v>
-      </c>
-      <c r="K14" t="n">
-        <v>494.7921626620081</v>
-      </c>
-      <c r="L14" t="n">
-        <v>48.28001747222002</v>
-      </c>
-      <c r="M14" t="n">
-        <v>492.9168657099305</v>
-      </c>
-      <c r="N14" t="n">
-        <v>51.61641752063617</v>
-      </c>
-      <c r="O14" t="n">
-        <v>493.1560944755785</v>
-      </c>
-      <c r="P14" t="n">
-        <v>43.36079627255683</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>497.6643800460207</v>
-      </c>
       <c r="R14" t="n">
-        <v>44.09392863184471</v>
+        <v>473.87</v>
       </c>
       <c r="S14" t="n">
-        <v>501.0719034886019</v>
+        <v>47.58</v>
       </c>
       <c r="T14" t="n">
-        <v>43.93143899014127</v>
+        <v>494.79</v>
       </c>
       <c r="U14" t="n">
-        <v>500.534297144295</v>
+        <v>48.28</v>
       </c>
       <c r="V14" t="n">
-        <v>43.99819800137994</v>
+        <v>492.92</v>
       </c>
       <c r="W14" t="n">
-        <v>503.6907961360603</v>
+        <v>51.62</v>
       </c>
       <c r="X14" t="n">
-        <v>43.61957221968848</v>
+        <v>493.16</v>
       </c>
       <c r="Y14" t="n">
-        <v>500.3986648026987</v>
+        <v>43.36</v>
       </c>
       <c r="Z14" t="n">
-        <v>47.54995847949419</v>
+        <v>497.66</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>44.09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>501.07</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>43.93</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>500.53</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>503.69</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>43.62</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>500.4</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>47.55</v>
       </c>
       <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
         <v>502.45</v>
       </c>
-      <c r="AK14" t="n">
+      <c r="AT14" t="n">
         <v>499.7333333333333</v>
       </c>
-      <c r="AL14" t="n">
+      <c r="AU14" t="n">
         <v>499.725</v>
       </c>
-      <c r="AM14" t="n">
+      <c r="AV14" t="n">
         <v>498.57</v>
       </c>
-      <c r="AN14" t="n">
+      <c r="AW14" t="n">
         <v>497.8416666666666</v>
       </c>
-      <c r="AO14" t="n">
+      <c r="AX14" t="n">
         <v>497.6214285714286</v>
       </c>
-      <c r="AP14" t="n">
+      <c r="AY14" t="n">
         <v>497.55</v>
       </c>
-      <c r="AQ14" t="n">
+      <c r="AZ14" t="n">
         <v>497.2333333333333</v>
       </c>
-      <c r="AR14" t="n">
+      <c r="BA14" t="n">
         <v>497.025</v>
       </c>
-      <c r="AS14" t="n">
+      <c r="BB14" t="n">
         <v>75.12421380620232</v>
       </c>
-      <c r="AT14" t="n">
+      <c r="BC14" t="n">
         <v>69.75764394594249</v>
       </c>
-      <c r="AU14" t="n">
+      <c r="BD14" t="n">
         <v>65.75902504599654</v>
       </c>
-      <c r="AV14" t="n">
+      <c r="BE14" t="n">
         <v>64.07046979693531</v>
       </c>
-      <c r="AW14" t="n">
+      <c r="BF14" t="n">
         <v>62.30074850183495</v>
       </c>
-      <c r="AX14" t="n">
+      <c r="BG14" t="n">
         <v>60.64692523794035</v>
       </c>
-      <c r="AY14" t="n">
+      <c r="BH14" t="n">
         <v>58.96882651028423</v>
       </c>
-      <c r="AZ14" t="n">
+      <c r="BI14" t="n">
         <v>57.25674147595586</v>
       </c>
-      <c r="BA14" t="n">
+      <c r="BJ14" t="n">
         <v>56.07784210363305</v>
       </c>
-      <c r="BB14" t="n">
+      <c r="BK14" t="n">
         <v>338</v>
       </c>
-      <c r="BC14" t="n">
+      <c r="BL14" t="n">
         <v>338</v>
       </c>
-      <c r="BD14" t="n">
+      <c r="BM14" t="n">
         <v>338</v>
       </c>
-      <c r="BE14" t="n">
+      <c r="BN14" t="n">
         <v>338</v>
       </c>
-      <c r="BF14" t="n">
+      <c r="BO14" t="n">
         <v>338</v>
       </c>
-      <c r="BG14" t="n">
+      <c r="BP14" t="n">
         <v>338</v>
       </c>
-      <c r="BH14" t="n">
+      <c r="BQ14" t="n">
         <v>338</v>
       </c>
-      <c r="BI14" t="n">
+      <c r="BR14" t="n">
         <v>338</v>
       </c>
-      <c r="BJ14" t="n">
+      <c r="BS14" t="n">
         <v>338</v>
       </c>
-      <c r="BK14" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ14" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR14" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>669</v>
-      </c>
       <c r="BT14" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB14" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC14" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="BU14" t="n">
+      <c r="CD14" t="n">
         <v>0.7777777777777778</v>
       </c>
-      <c r="BV14" t="n">
+      <c r="CE14" t="n">
         <v>0.8214285714285714</v>
       </c>
-      <c r="BW14" t="n">
+      <c r="CF14" t="n">
         <v>0.7105263157894737</v>
       </c>
-      <c r="BX14" t="n">
+      <c r="CG14" t="n">
         <v>0.6875</v>
       </c>
-      <c r="BY14" t="n">
+      <c r="CH14" t="n">
         <v>0.7068965517241379</v>
       </c>
-      <c r="BZ14" t="n">
+      <c r="CI14" t="n">
         <v>0.6470588235294118</v>
       </c>
-      <c r="CA14" t="n">
+      <c r="CJ14" t="n">
         <v>0.704225352112676</v>
       </c>
-      <c r="CB14" t="n">
+      <c r="CK14" t="n">
         <v>0.7466666666666667</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>500.4</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>47.55</v>
       </c>
     </row>
     <row r="15">
@@ -4038,10 +4522,10 @@
         <v>500</v>
       </c>
       <c r="C15" t="n">
+        <v>62.26834692364714</v>
+      </c>
+      <c r="D15" t="n">
         <v>42</v>
-      </c>
-      <c r="D15" t="n">
-        <v>62.26834692364714</v>
       </c>
       <c r="E15" t="n">
         <v>500</v>
@@ -4050,228 +4534,261 @@
         <v>200</v>
       </c>
       <c r="G15" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="H15" t="inlineStr">
+        <v>81</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="Q15" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I15" t="n">
-        <v>523.8617380302941</v>
-      </c>
-      <c r="J15" t="n">
-        <v>60.22736696792596</v>
-      </c>
-      <c r="K15" t="n">
-        <v>522.3081900779845</v>
-      </c>
-      <c r="L15" t="n">
-        <v>46.24638288307652</v>
-      </c>
-      <c r="M15" t="n">
-        <v>504.4743862200624</v>
-      </c>
-      <c r="N15" t="n">
-        <v>44.89172621583305</v>
-      </c>
-      <c r="O15" t="n">
-        <v>499.9351955262771</v>
-      </c>
-      <c r="P15" t="n">
-        <v>43.80730814887184</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>491.9210094188181</v>
-      </c>
       <c r="R15" t="n">
-        <v>51.07771750651959</v>
+        <v>523.86</v>
       </c>
       <c r="S15" t="n">
-        <v>491.7586101691186</v>
+        <v>60.23</v>
       </c>
       <c r="T15" t="n">
-        <v>48.58228864034698</v>
+        <v>522.3099999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>488.3430618786534</v>
+        <v>46.25</v>
       </c>
       <c r="V15" t="n">
-        <v>45.0055364701254</v>
+        <v>504.47</v>
       </c>
       <c r="W15" t="n">
-        <v>492.8239259048069</v>
+        <v>44.89</v>
       </c>
       <c r="X15" t="n">
-        <v>49.66926046631222</v>
+        <v>499.94</v>
       </c>
       <c r="Y15" t="n">
-        <v>493.0188391591717</v>
+        <v>43.81</v>
       </c>
       <c r="Z15" t="n">
-        <v>49.5502422898256</v>
+        <v>491.92</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>51.08</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>491.76</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>48.58</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>488.34</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>45.01</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>492.82</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>49.67</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>493.02</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>49.55</v>
       </c>
       <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
         <v>528.1</v>
       </c>
-      <c r="AK15" t="n">
+      <c r="AT15" t="n">
         <v>529.35</v>
       </c>
-      <c r="AL15" t="n">
+      <c r="AU15" t="n">
         <v>526.2375</v>
       </c>
-      <c r="AM15" t="n">
+      <c r="AV15" t="n">
         <v>520.16</v>
       </c>
-      <c r="AN15" t="n">
+      <c r="AW15" t="n">
         <v>512.95</v>
       </c>
-      <c r="AO15" t="n">
+      <c r="AX15" t="n">
         <v>507.8</v>
       </c>
-      <c r="AP15" t="n">
+      <c r="AY15" t="n">
         <v>503.41875</v>
       </c>
-      <c r="AQ15" t="n">
+      <c r="AZ15" t="n">
         <v>501.4166666666667</v>
       </c>
-      <c r="AR15" t="n">
+      <c r="BA15" t="n">
         <v>500.85</v>
       </c>
-      <c r="AS15" t="n">
+      <c r="BB15" t="n">
         <v>86.19970997631025</v>
       </c>
-      <c r="AT15" t="n">
+      <c r="BC15" t="n">
         <v>77.73240958570628</v>
       </c>
-      <c r="AU15" t="n">
+      <c r="BD15" t="n">
         <v>69.80208516763665</v>
       </c>
-      <c r="AV15" t="n">
+      <c r="BE15" t="n">
         <v>65.06746037767263</v>
       </c>
-      <c r="AW15" t="n">
+      <c r="BF15" t="n">
         <v>64.79967206707146</v>
       </c>
-      <c r="AX15" t="n">
+      <c r="BG15" t="n">
         <v>64.61636236832189</v>
       </c>
-      <c r="AY15" t="n">
+      <c r="BH15" t="n">
         <v>64.33442623073202</v>
       </c>
-      <c r="AZ15" t="n">
+      <c r="BI15" t="n">
         <v>64.90761597155692</v>
       </c>
-      <c r="BA15" t="n">
+      <c r="BJ15" t="n">
         <v>67.17356250787954</v>
       </c>
-      <c r="BB15" t="n">
+      <c r="BK15" t="n">
         <v>329</v>
       </c>
-      <c r="BC15" t="n">
+      <c r="BL15" t="n">
         <v>329</v>
       </c>
-      <c r="BD15" t="n">
+      <c r="BM15" t="n">
         <v>329</v>
       </c>
-      <c r="BE15" t="n">
+      <c r="BN15" t="n">
         <v>329</v>
       </c>
-      <c r="BF15" t="n">
+      <c r="BO15" t="n">
         <v>329</v>
       </c>
-      <c r="BG15" t="n">
+      <c r="BP15" t="n">
         <v>329</v>
       </c>
-      <c r="BH15" t="n">
+      <c r="BQ15" t="n">
         <v>329</v>
       </c>
-      <c r="BI15" t="n">
+      <c r="BR15" t="n">
         <v>329</v>
       </c>
-      <c r="BJ15" t="n">
+      <c r="BS15" t="n">
         <v>329</v>
       </c>
-      <c r="BK15" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ15" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR15" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS15" t="n">
-        <v>669</v>
-      </c>
       <c r="BT15" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB15" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC15" t="n">
         <v>0.75</v>
       </c>
-      <c r="BU15" t="n">
+      <c r="CD15" t="n">
         <v>0.8461538461538461</v>
       </c>
-      <c r="BV15" t="n">
+      <c r="CE15" t="n">
         <v>0.6875</v>
       </c>
-      <c r="BW15" t="n">
+      <c r="CF15" t="n">
         <v>0.5238095238095238</v>
       </c>
-      <c r="BX15" t="n">
+      <c r="CG15" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="BY15" t="n">
+      <c r="CH15" t="n">
         <v>0.875</v>
       </c>
-      <c r="BZ15" t="n">
+      <c r="CI15" t="n">
         <v>0.65625</v>
       </c>
-      <c r="CA15" t="n">
+      <c r="CJ15" t="n">
         <v>0.6176470588235294</v>
       </c>
-      <c r="CB15" t="n">
+      <c r="CK15" t="n">
         <v>0.7647058823529411</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>493.02</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>49.55</v>
       </c>
     </row>
     <row r="16">
@@ -4284,10 +4801,10 @@
         <v>498</v>
       </c>
       <c r="C16" t="n">
+        <v>59.30318754633062</v>
+      </c>
+      <c r="D16" t="n">
         <v>40</v>
-      </c>
-      <c r="D16" t="n">
-        <v>59.30318754633062</v>
       </c>
       <c r="E16" t="n">
         <v>498</v>
@@ -4296,228 +4813,261 @@
         <v>200</v>
       </c>
       <c r="G16" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="H16" t="inlineStr">
+        <v>80</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I16" t="n">
-        <v>470.3774642306424</v>
-      </c>
-      <c r="J16" t="n">
-        <v>60.70604211000657</v>
-      </c>
-      <c r="K16" t="n">
-        <v>488.5198242284661</v>
-      </c>
-      <c r="L16" t="n">
-        <v>55.37435862392427</v>
-      </c>
-      <c r="M16" t="n">
-        <v>487.9665021808999</v>
-      </c>
-      <c r="N16" t="n">
-        <v>53.85270389343314</v>
-      </c>
-      <c r="O16" t="n">
-        <v>497.4019381940029</v>
-      </c>
-      <c r="P16" t="n">
-        <v>50.2086839014237</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>491.1501044218243</v>
-      </c>
       <c r="R16" t="n">
-        <v>48.9754768433509</v>
+        <v>470.38</v>
       </c>
       <c r="S16" t="n">
-        <v>490.6575745521315</v>
+        <v>60.71</v>
       </c>
       <c r="T16" t="n">
-        <v>50.22830370570026</v>
+        <v>488.52</v>
       </c>
       <c r="U16" t="n">
-        <v>492.2900262604841</v>
+        <v>55.37</v>
       </c>
       <c r="V16" t="n">
-        <v>49.71059793747221</v>
+        <v>487.97</v>
       </c>
       <c r="W16" t="n">
-        <v>492.1420178696582</v>
+        <v>53.85</v>
       </c>
       <c r="X16" t="n">
-        <v>48.000907154853</v>
+        <v>497.4</v>
       </c>
       <c r="Y16" t="n">
-        <v>490.2213665812172</v>
+        <v>50.21</v>
       </c>
       <c r="Z16" t="n">
-        <v>49.82711058021088</v>
+        <v>491.15</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>48.98</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>490.66</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>50.23</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>492.29</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>49.71</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>492.14</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>490.22</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>49.83</v>
       </c>
       <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
         <v>497.4</v>
       </c>
-      <c r="AK16" t="n">
+      <c r="AT16" t="n">
         <v>489.1166666666667</v>
       </c>
-      <c r="AL16" t="n">
+      <c r="AU16" t="n">
         <v>488.6125</v>
       </c>
-      <c r="AM16" t="n">
+      <c r="AV16" t="n">
         <v>489.11</v>
       </c>
-      <c r="AN16" t="n">
+      <c r="AW16" t="n">
         <v>490.8</v>
       </c>
-      <c r="AO16" t="n">
+      <c r="AX16" t="n">
         <v>490.3142857142857</v>
       </c>
-      <c r="AP16" t="n">
+      <c r="AY16" t="n">
         <v>491.81875</v>
       </c>
-      <c r="AQ16" t="n">
+      <c r="AZ16" t="n">
         <v>493.0277777777778</v>
       </c>
-      <c r="AR16" t="n">
+      <c r="BA16" t="n">
         <v>493.56</v>
       </c>
-      <c r="AS16" t="n">
+      <c r="BB16" t="n">
         <v>104.2923295357813</v>
       </c>
-      <c r="AT16" t="n">
+      <c r="BC16" t="n">
         <v>92.91395511738565</v>
       </c>
-      <c r="AU16" t="n">
+      <c r="BD16" t="n">
         <v>84.41038054498985</v>
       </c>
-      <c r="AV16" t="n">
+      <c r="BE16" t="n">
         <v>78.00293520118329</v>
       </c>
-      <c r="AW16" t="n">
+      <c r="BF16" t="n">
         <v>73.43507336416299</v>
       </c>
-      <c r="AX16" t="n">
+      <c r="BG16" t="n">
         <v>70.6287159036895</v>
       </c>
-      <c r="AY16" t="n">
+      <c r="BH16" t="n">
         <v>68.87351376572491</v>
       </c>
-      <c r="AZ16" t="n">
+      <c r="BI16" t="n">
         <v>67.45059348685076</v>
       </c>
-      <c r="BA16" t="n">
+      <c r="BJ16" t="n">
         <v>66.34136266312292</v>
       </c>
-      <c r="BB16" t="n">
+      <c r="BK16" t="n">
         <v>329</v>
       </c>
-      <c r="BC16" t="n">
+      <c r="BL16" t="n">
         <v>329</v>
       </c>
-      <c r="BD16" t="n">
+      <c r="BM16" t="n">
         <v>329</v>
       </c>
-      <c r="BE16" t="n">
+      <c r="BN16" t="n">
         <v>329</v>
       </c>
-      <c r="BF16" t="n">
+      <c r="BO16" t="n">
         <v>329</v>
       </c>
-      <c r="BG16" t="n">
+      <c r="BP16" t="n">
         <v>329</v>
       </c>
-      <c r="BH16" t="n">
+      <c r="BQ16" t="n">
         <v>329</v>
       </c>
-      <c r="BI16" t="n">
+      <c r="BR16" t="n">
         <v>329</v>
       </c>
-      <c r="BJ16" t="n">
+      <c r="BS16" t="n">
         <v>329</v>
       </c>
-      <c r="BK16" t="n">
+      <c r="BT16" t="n">
         <v>675</v>
       </c>
-      <c r="BL16" t="n">
+      <c r="BU16" t="n">
         <v>675</v>
       </c>
-      <c r="BM16" t="n">
+      <c r="BV16" t="n">
         <v>675</v>
       </c>
-      <c r="BN16" t="n">
+      <c r="BW16" t="n">
         <v>675</v>
       </c>
-      <c r="BO16" t="n">
+      <c r="BX16" t="n">
         <v>675</v>
       </c>
-      <c r="BP16" t="n">
+      <c r="BY16" t="n">
         <v>675</v>
       </c>
-      <c r="BQ16" t="n">
+      <c r="BZ16" t="n">
         <v>675</v>
       </c>
-      <c r="BR16" t="n">
+      <c r="CA16" t="n">
         <v>675</v>
       </c>
-      <c r="BS16" t="n">
+      <c r="CB16" t="n">
         <v>675</v>
       </c>
-      <c r="BT16" t="n">
+      <c r="CC16" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="BU16" t="n">
+      <c r="CD16" t="n">
         <v>0.9166666666666666</v>
       </c>
-      <c r="BV16" t="n">
+      <c r="CE16" t="n">
         <v>0.8666666666666667</v>
       </c>
-      <c r="BW16" t="n">
+      <c r="CF16" t="n">
         <v>0.5833333333333334</v>
       </c>
-      <c r="BX16" t="n">
+      <c r="CG16" t="n">
         <v>0.64</v>
       </c>
-      <c r="BY16" t="n">
+      <c r="CH16" t="n">
         <v>0.625</v>
       </c>
-      <c r="BZ16" t="n">
+      <c r="CI16" t="n">
         <v>0.6875</v>
       </c>
-      <c r="CA16" t="n">
+      <c r="CJ16" t="n">
         <v>0.90625</v>
       </c>
-      <c r="CB16" t="n">
+      <c r="CK16" t="n">
         <v>0.9444444444444444</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>490.22</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>49.83</v>
       </c>
     </row>
     <row r="17">
@@ -4530,10 +5080,10 @@
         <v>501</v>
       </c>
       <c r="C17" t="n">
+        <v>62.26834692364714</v>
+      </c>
+      <c r="D17" t="n">
         <v>42</v>
-      </c>
-      <c r="D17" t="n">
-        <v>62.26834692364714</v>
       </c>
       <c r="E17" t="n">
         <v>501</v>
@@ -4542,228 +5092,261 @@
         <v>200</v>
       </c>
       <c r="G17" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="H17" t="inlineStr">
+        <v>80.5</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="M17" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="Q17" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I17" t="n">
-        <v>490.244897216839</v>
-      </c>
-      <c r="J17" t="n">
-        <v>48.6599171875196</v>
-      </c>
-      <c r="K17" t="n">
-        <v>498.9052739392008</v>
-      </c>
-      <c r="L17" t="n">
-        <v>54.99781533393917</v>
-      </c>
-      <c r="M17" t="n">
-        <v>491.936676891634</v>
-      </c>
-      <c r="N17" t="n">
-        <v>53.01436299525211</v>
-      </c>
-      <c r="O17" t="n">
-        <v>504.2410490018805</v>
-      </c>
-      <c r="P17" t="n">
-        <v>58.16858145525397</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>500.9764613504212</v>
-      </c>
       <c r="R17" t="n">
-        <v>59.15161887879982</v>
+        <v>490.24</v>
       </c>
       <c r="S17" t="n">
-        <v>502.556989064208</v>
+        <v>48.66</v>
       </c>
       <c r="T17" t="n">
-        <v>59.37984298280674</v>
+        <v>498.91</v>
       </c>
       <c r="U17" t="n">
-        <v>496.8227233777552</v>
+        <v>55</v>
       </c>
       <c r="V17" t="n">
-        <v>57.29537596105637</v>
+        <v>491.94</v>
       </c>
       <c r="W17" t="n">
-        <v>492.6252377026085</v>
+        <v>53.01</v>
       </c>
       <c r="X17" t="n">
-        <v>54.41250592043651</v>
+        <v>504.24</v>
       </c>
       <c r="Y17" t="n">
-        <v>492.2332353751932</v>
+        <v>58.17</v>
       </c>
       <c r="Z17" t="n">
-        <v>52.22549302890991</v>
+        <v>500.98</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>59.15</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>502.56</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>59.38</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>496.82</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>57.3</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>492.63</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>54.41</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>492.23</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>52.23</v>
       </c>
       <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
         <v>483.05</v>
       </c>
-      <c r="AK17" t="n">
+      <c r="AT17" t="n">
         <v>489.1833333333333</v>
       </c>
-      <c r="AL17" t="n">
+      <c r="AU17" t="n">
         <v>491.575</v>
       </c>
-      <c r="AM17" t="n">
+      <c r="AV17" t="n">
         <v>492.76</v>
       </c>
-      <c r="AN17" t="n">
+      <c r="AW17" t="n">
         <v>496.2916666666667</v>
       </c>
-      <c r="AO17" t="n">
+      <c r="AX17" t="n">
         <v>498.5785714285714</v>
       </c>
-      <c r="AP17" t="n">
+      <c r="AY17" t="n">
         <v>498.88125</v>
       </c>
-      <c r="AQ17" t="n">
+      <c r="AZ17" t="n">
         <v>498</v>
       </c>
-      <c r="AR17" t="n">
+      <c r="BA17" t="n">
         <v>497.545</v>
       </c>
-      <c r="AS17" t="n">
+      <c r="BB17" t="n">
         <v>82.59054122597817</v>
       </c>
-      <c r="AT17" t="n">
+      <c r="BC17" t="n">
         <v>77.02066641853702</v>
       </c>
-      <c r="AU17" t="n">
+      <c r="BD17" t="n">
         <v>72.33425450642316</v>
       </c>
-      <c r="AV17" t="n">
+      <c r="BE17" t="n">
         <v>69.37782354614477</v>
       </c>
-      <c r="AW17" t="n">
+      <c r="BF17" t="n">
         <v>70.37890259556166</v>
       </c>
-      <c r="AX17" t="n">
+      <c r="BG17" t="n">
         <v>70.4484682847929</v>
       </c>
-      <c r="AY17" t="n">
+      <c r="BH17" t="n">
         <v>69.90568394942933</v>
       </c>
-      <c r="AZ17" t="n">
+      <c r="BI17" t="n">
         <v>68.23382999330725</v>
       </c>
-      <c r="BA17" t="n">
+      <c r="BJ17" t="n">
         <v>67.0695010791045</v>
       </c>
-      <c r="BB17" t="n">
+      <c r="BK17" t="n">
         <v>327</v>
       </c>
-      <c r="BC17" t="n">
+      <c r="BL17" t="n">
         <v>327</v>
       </c>
-      <c r="BD17" t="n">
+      <c r="BM17" t="n">
         <v>327</v>
       </c>
-      <c r="BE17" t="n">
+      <c r="BN17" t="n">
         <v>327</v>
       </c>
-      <c r="BF17" t="n">
+      <c r="BO17" t="n">
         <v>327</v>
       </c>
-      <c r="BG17" t="n">
+      <c r="BP17" t="n">
         <v>327</v>
       </c>
-      <c r="BH17" t="n">
+      <c r="BQ17" t="n">
         <v>327</v>
       </c>
-      <c r="BI17" t="n">
+      <c r="BR17" t="n">
         <v>327</v>
       </c>
-      <c r="BJ17" t="n">
+      <c r="BS17" t="n">
         <v>327</v>
       </c>
-      <c r="BK17" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP17" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ17" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR17" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS17" t="n">
-        <v>669</v>
-      </c>
       <c r="BT17" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB17" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC17" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="BU17" t="n">
+      <c r="CD17" t="n">
         <v>0.75</v>
       </c>
-      <c r="BV17" t="n">
+      <c r="CE17" t="n">
         <v>0.7777777777777778</v>
       </c>
-      <c r="BW17" t="n">
+      <c r="CF17" t="n">
         <v>0.9565217391304348</v>
       </c>
-      <c r="BX17" t="n">
+      <c r="CG17" t="n">
         <v>0.7586206896551724</v>
       </c>
-      <c r="BY17" t="n">
+      <c r="CH17" t="n">
         <v>0.8387096774193549</v>
       </c>
-      <c r="BZ17" t="n">
+      <c r="CI17" t="n">
         <v>0.75</v>
       </c>
-      <c r="CA17" t="n">
+      <c r="CJ17" t="n">
         <v>0.6923076923076923</v>
       </c>
-      <c r="CB17" t="n">
+      <c r="CK17" t="n">
         <v>0.675</v>
+      </c>
+      <c r="CL17" t="n">
+        <v>492.23</v>
+      </c>
+      <c r="CM17" t="n">
+        <v>52.23</v>
       </c>
     </row>
     <row r="18">
@@ -4776,10 +5359,10 @@
         <v>500</v>
       </c>
       <c r="C18" t="n">
+        <v>62.26834692364714</v>
+      </c>
+      <c r="D18" t="n">
         <v>42</v>
-      </c>
-      <c r="D18" t="n">
-        <v>62.26834692364714</v>
       </c>
       <c r="E18" t="n">
         <v>500</v>
@@ -4788,228 +5371,261 @@
         <v>200</v>
       </c>
       <c r="G18" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="H18" t="inlineStr">
+        <v>80.5</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q18" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I18" t="n">
-        <v>481.2099559285311</v>
-      </c>
-      <c r="J18" t="n">
-        <v>42.8616396531366</v>
-      </c>
-      <c r="K18" t="n">
-        <v>486.0083204708175</v>
-      </c>
-      <c r="L18" t="n">
-        <v>45.40573661102076</v>
-      </c>
-      <c r="M18" t="n">
-        <v>486.64402040256</v>
-      </c>
-      <c r="N18" t="n">
-        <v>45.89484119896066</v>
-      </c>
-      <c r="O18" t="n">
-        <v>488.2022334137228</v>
-      </c>
-      <c r="P18" t="n">
-        <v>49.33289659126429</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>486.7393556706874</v>
-      </c>
       <c r="R18" t="n">
-        <v>47.62175844660543</v>
+        <v>481.21</v>
       </c>
       <c r="S18" t="n">
-        <v>492.5318289281931</v>
+        <v>42.86</v>
       </c>
       <c r="T18" t="n">
-        <v>49.12191847108716</v>
+        <v>486.01</v>
       </c>
       <c r="U18" t="n">
-        <v>497.5390895936566</v>
+        <v>45.41</v>
       </c>
       <c r="V18" t="n">
-        <v>47.69604770291934</v>
+        <v>486.64</v>
       </c>
       <c r="W18" t="n">
-        <v>498.5748110029872</v>
+        <v>45.89</v>
       </c>
       <c r="X18" t="n">
-        <v>43.37012021134642</v>
+        <v>488.2</v>
       </c>
       <c r="Y18" t="n">
-        <v>497.734003963115</v>
+        <v>49.33</v>
       </c>
       <c r="Z18" t="n">
-        <v>44.46645118303814</v>
+        <v>486.74</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>47.62</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>492.53</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>49.12</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>497.54</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>47.7</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>498.57</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>43.37</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>497.73</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>44.47</v>
       </c>
       <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
         <v>497.2</v>
       </c>
-      <c r="AK18" t="n">
+      <c r="AT18" t="n">
         <v>495.65</v>
       </c>
-      <c r="AL18" t="n">
+      <c r="AU18" t="n">
         <v>493.7375</v>
       </c>
-      <c r="AM18" t="n">
+      <c r="AV18" t="n">
         <v>493.61</v>
       </c>
-      <c r="AN18" t="n">
+      <c r="AW18" t="n">
         <v>493.2083333333333</v>
       </c>
-      <c r="AO18" t="n">
+      <c r="AX18" t="n">
         <v>492.7214285714286</v>
       </c>
-      <c r="AP18" t="n">
+      <c r="AY18" t="n">
         <v>493.05625</v>
       </c>
-      <c r="AQ18" t="n">
+      <c r="AZ18" t="n">
         <v>494.3166666666667</v>
       </c>
-      <c r="AR18" t="n">
+      <c r="BA18" t="n">
         <v>495.765</v>
       </c>
-      <c r="AS18" t="n">
+      <c r="BB18" t="n">
         <v>78.23400795050705</v>
       </c>
-      <c r="AT18" t="n">
+      <c r="BC18" t="n">
         <v>70.30785280938869</v>
       </c>
-      <c r="AU18" t="n">
+      <c r="BD18" t="n">
         <v>66.71539247992176</v>
       </c>
-      <c r="AV18" t="n">
+      <c r="BE18" t="n">
         <v>63.61963454783437</v>
       </c>
-      <c r="AW18" t="n">
+      <c r="BF18" t="n">
         <v>61.7384126555115</v>
       </c>
-      <c r="AX18" t="n">
+      <c r="BG18" t="n">
         <v>60.44207000534158</v>
       </c>
-      <c r="AY18" t="n">
+      <c r="BH18" t="n">
         <v>59.2277644853957</v>
       </c>
-      <c r="AZ18" t="n">
+      <c r="BI18" t="n">
         <v>57.57627549607564</v>
       </c>
-      <c r="BA18" t="n">
+      <c r="BJ18" t="n">
         <v>55.72171726535355</v>
       </c>
-      <c r="BB18" t="n">
+      <c r="BK18" t="n">
         <v>330</v>
       </c>
-      <c r="BC18" t="n">
+      <c r="BL18" t="n">
         <v>330</v>
       </c>
-      <c r="BD18" t="n">
+      <c r="BM18" t="n">
         <v>330</v>
       </c>
-      <c r="BE18" t="n">
+      <c r="BN18" t="n">
         <v>330</v>
       </c>
-      <c r="BF18" t="n">
+      <c r="BO18" t="n">
         <v>330</v>
       </c>
-      <c r="BG18" t="n">
+      <c r="BP18" t="n">
         <v>330</v>
       </c>
-      <c r="BH18" t="n">
+      <c r="BQ18" t="n">
         <v>330</v>
       </c>
-      <c r="BI18" t="n">
+      <c r="BR18" t="n">
         <v>330</v>
       </c>
-      <c r="BJ18" t="n">
+      <c r="BS18" t="n">
         <v>330</v>
       </c>
-      <c r="BK18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS18" t="n">
-        <v>669</v>
-      </c>
       <c r="BT18" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB18" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC18" t="n">
         <v>0.8888888888888888</v>
       </c>
-      <c r="BU18" t="n">
+      <c r="CD18" t="n">
         <v>0.8235294117647058</v>
       </c>
-      <c r="BV18" t="n">
+      <c r="CE18" t="n">
         <v>0.7407407407407407</v>
       </c>
-      <c r="BW18" t="n">
+      <c r="CF18" t="n">
         <v>0.7027027027027027</v>
       </c>
-      <c r="BX18" t="n">
+      <c r="CG18" t="n">
         <v>0.6808510638297872</v>
       </c>
-      <c r="BY18" t="n">
+      <c r="CH18" t="n">
         <v>0.6140350877192983</v>
       </c>
-      <c r="BZ18" t="n">
+      <c r="CI18" t="n">
         <v>0.6119402985074627</v>
       </c>
-      <c r="CA18" t="n">
+      <c r="CJ18" t="n">
         <v>0.5324675324675324</v>
       </c>
-      <c r="CB18" t="n">
+      <c r="CK18" t="n">
         <v>0.4712643678160919</v>
+      </c>
+      <c r="CL18" t="n">
+        <v>497.73</v>
+      </c>
+      <c r="CM18" t="n">
+        <v>44.47</v>
       </c>
     </row>
     <row r="19">
@@ -5022,10 +5638,10 @@
         <v>500</v>
       </c>
       <c r="C19" t="n">
+        <v>57.82060785767235</v>
+      </c>
+      <c r="D19" t="n">
         <v>39</v>
-      </c>
-      <c r="D19" t="n">
-        <v>57.82060785767235</v>
       </c>
       <c r="E19" t="n">
         <v>500</v>
@@ -5034,228 +5650,261 @@
         <v>200</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H19" t="inlineStr">
+        <v>80</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="M19" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Q19" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I19" t="n">
-        <v>511.9473557585039</v>
-      </c>
-      <c r="J19" t="n">
-        <v>43.7176041909316</v>
-      </c>
-      <c r="K19" t="n">
-        <v>518.6133672547346</v>
-      </c>
-      <c r="L19" t="n">
-        <v>40.87891169904707</v>
-      </c>
-      <c r="M19" t="n">
-        <v>516.1357569835712</v>
-      </c>
-      <c r="N19" t="n">
-        <v>55.19034282484099</v>
-      </c>
-      <c r="O19" t="n">
-        <v>508.8217721427376</v>
-      </c>
-      <c r="P19" t="n">
-        <v>50.84399220982549</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>509.0658520559606</v>
-      </c>
       <c r="R19" t="n">
-        <v>55.77617576425357</v>
+        <v>511.95</v>
       </c>
       <c r="S19" t="n">
-        <v>510.7225708896362</v>
+        <v>43.72</v>
       </c>
       <c r="T19" t="n">
-        <v>56.47149736908951</v>
+        <v>518.61</v>
       </c>
       <c r="U19" t="n">
-        <v>511.8875614020186</v>
+        <v>40.88</v>
       </c>
       <c r="V19" t="n">
-        <v>57.10194844809575</v>
+        <v>516.14</v>
       </c>
       <c r="W19" t="n">
-        <v>509.7543529297197</v>
+        <v>55.19</v>
       </c>
       <c r="X19" t="n">
-        <v>57.85012581554644</v>
+        <v>508.82</v>
       </c>
       <c r="Y19" t="n">
-        <v>507.5110108296814</v>
+        <v>50.84</v>
       </c>
       <c r="Z19" t="n">
-        <v>56.45592105984905</v>
+        <v>509.07</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>55.78</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>510.72</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>56.47</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>511.89</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>57.1</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>509.75</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>57.85</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>507.51</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>56.46</v>
       </c>
       <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
         <v>518.625</v>
       </c>
-      <c r="AK19" t="n">
+      <c r="AT19" t="n">
         <v>517.8</v>
       </c>
-      <c r="AL19" t="n">
+      <c r="AU19" t="n">
         <v>515.4625</v>
       </c>
-      <c r="AM19" t="n">
+      <c r="AV19" t="n">
         <v>510.32</v>
       </c>
-      <c r="AN19" t="n">
+      <c r="AW19" t="n">
         <v>505.8416666666666</v>
       </c>
-      <c r="AO19" t="n">
+      <c r="AX19" t="n">
         <v>503.3571428571428</v>
       </c>
-      <c r="AP19" t="n">
+      <c r="AY19" t="n">
         <v>503.28125</v>
       </c>
-      <c r="AQ19" t="n">
+      <c r="AZ19" t="n">
         <v>505.0944444444444</v>
       </c>
-      <c r="AR19" t="n">
+      <c r="BA19" t="n">
         <v>505.985</v>
       </c>
-      <c r="AS19" t="n">
+      <c r="BB19" t="n">
         <v>86.0498946832592</v>
       </c>
-      <c r="AT19" t="n">
+      <c r="BC19" t="n">
         <v>75.44574209324209</v>
       </c>
-      <c r="AU19" t="n">
+      <c r="BD19" t="n">
         <v>71.43352569872216</v>
       </c>
-      <c r="AV19" t="n">
+      <c r="BE19" t="n">
         <v>72.34471369768492</v>
       </c>
-      <c r="AW19" t="n">
+      <c r="BF19" t="n">
         <v>71.38744005231048</v>
       </c>
-      <c r="AX19" t="n">
+      <c r="BG19" t="n">
         <v>72.45225732740654</v>
       </c>
-      <c r="AY19" t="n">
+      <c r="BH19" t="n">
         <v>74.10720038186236</v>
       </c>
-      <c r="AZ19" t="n">
+      <c r="BI19" t="n">
         <v>73.55977895730052</v>
       </c>
-      <c r="BA19" t="n">
+      <c r="BJ19" t="n">
         <v>72.32430279650126</v>
       </c>
-      <c r="BB19" t="n">
+      <c r="BK19" t="n">
         <v>318</v>
       </c>
-      <c r="BC19" t="n">
+      <c r="BL19" t="n">
         <v>318</v>
       </c>
-      <c r="BD19" t="n">
+      <c r="BM19" t="n">
         <v>318</v>
       </c>
-      <c r="BE19" t="n">
+      <c r="BN19" t="n">
         <v>318</v>
       </c>
-      <c r="BF19" t="n">
+      <c r="BO19" t="n">
         <v>318</v>
       </c>
-      <c r="BG19" t="n">
+      <c r="BP19" t="n">
         <v>318</v>
       </c>
-      <c r="BH19" t="n">
+      <c r="BQ19" t="n">
         <v>318</v>
       </c>
-      <c r="BI19" t="n">
+      <c r="BR19" t="n">
         <v>318</v>
       </c>
-      <c r="BJ19" t="n">
+      <c r="BS19" t="n">
         <v>318</v>
       </c>
-      <c r="BK19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS19" t="n">
-        <v>669</v>
-      </c>
       <c r="BT19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB19" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC19" t="n">
         <v>0.2</v>
       </c>
-      <c r="BU19" t="n">
+      <c r="CD19" t="n">
         <v>0.625</v>
       </c>
-      <c r="BV19" t="n">
+      <c r="CE19" t="n">
         <v>0.8421052631578947</v>
       </c>
-      <c r="BW19" t="n">
+      <c r="CF19" t="n">
         <v>0.9047619047619048</v>
       </c>
-      <c r="BX19" t="n">
+      <c r="CG19" t="n">
         <v>0.9047619047619048</v>
       </c>
-      <c r="BY19" t="n">
+      <c r="CH19" t="n">
         <v>0.8</v>
       </c>
-      <c r="BZ19" t="n">
+      <c r="CI19" t="n">
         <v>0.8846153846153846</v>
       </c>
-      <c r="CA19" t="n">
+      <c r="CJ19" t="n">
         <v>0.9259259259259259</v>
       </c>
-      <c r="CB19" t="n">
+      <c r="CK19" t="n">
         <v>0.8125</v>
+      </c>
+      <c r="CL19" t="n">
+        <v>507.51</v>
+      </c>
+      <c r="CM19" t="n">
+        <v>56.46</v>
       </c>
     </row>
     <row r="20">
@@ -5268,10 +5917,10 @@
         <v>502</v>
       </c>
       <c r="C20" t="n">
+        <v>60.78576723498888</v>
+      </c>
+      <c r="D20" t="n">
         <v>41</v>
-      </c>
-      <c r="D20" t="n">
-        <v>60.78576723498888</v>
       </c>
       <c r="E20" t="n">
         <v>502</v>
@@ -5280,228 +5929,261 @@
         <v>200</v>
       </c>
       <c r="G20" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="H20" t="inlineStr">
+        <v>79</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M20" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Q20" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I20" t="n">
-        <v>507.4746990603186</v>
-      </c>
-      <c r="J20" t="n">
-        <v>43.01016090793009</v>
-      </c>
-      <c r="K20" t="n">
-        <v>497.1948041884601</v>
-      </c>
-      <c r="L20" t="n">
-        <v>55.44527213145347</v>
-      </c>
-      <c r="M20" t="n">
-        <v>508.6783932101314</v>
-      </c>
-      <c r="N20" t="n">
-        <v>59.01371188283741</v>
-      </c>
-      <c r="O20" t="n">
-        <v>508.2167327842623</v>
-      </c>
-      <c r="P20" t="n">
-        <v>58.52206719363097</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>507.2014843441934</v>
-      </c>
       <c r="R20" t="n">
-        <v>54.11434172029926</v>
+        <v>507.47</v>
       </c>
       <c r="S20" t="n">
-        <v>507.5285228270888</v>
+        <v>43.01</v>
       </c>
       <c r="T20" t="n">
-        <v>53.38953322453766</v>
+        <v>497.19</v>
       </c>
       <c r="U20" t="n">
-        <v>502.900013988548</v>
+        <v>55.45</v>
       </c>
       <c r="V20" t="n">
-        <v>52.27067628198809</v>
+        <v>508.68</v>
       </c>
       <c r="W20" t="n">
-        <v>500.3497043591455</v>
+        <v>59.01</v>
       </c>
       <c r="X20" t="n">
-        <v>49.77109735141654</v>
+        <v>508.22</v>
       </c>
       <c r="Y20" t="n">
-        <v>500.2603989271763</v>
+        <v>58.52</v>
       </c>
       <c r="Z20" t="n">
-        <v>52.12506188979653</v>
+        <v>507.2</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>54.11</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>507.53</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>53.39</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>502.9</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>52.27</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>500.35</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>49.77</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>500.26</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>52.13</v>
       </c>
       <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
         <v>511.025</v>
       </c>
-      <c r="AK20" t="n">
+      <c r="AT20" t="n">
         <v>504.35</v>
       </c>
-      <c r="AL20" t="n">
+      <c r="AU20" t="n">
         <v>503.5</v>
       </c>
-      <c r="AM20" t="n">
+      <c r="AV20" t="n">
         <v>504.04</v>
       </c>
-      <c r="AN20" t="n">
+      <c r="AW20" t="n">
         <v>503.5083333333333</v>
       </c>
-      <c r="AO20" t="n">
+      <c r="AX20" t="n">
         <v>504.0285714285714</v>
       </c>
-      <c r="AP20" t="n">
+      <c r="AY20" t="n">
         <v>504.40625</v>
       </c>
-      <c r="AQ20" t="n">
+      <c r="AZ20" t="n">
         <v>503.15</v>
       </c>
-      <c r="AR20" t="n">
+      <c r="BA20" t="n">
         <v>501.71</v>
       </c>
-      <c r="AS20" t="n">
+      <c r="BB20" t="n">
         <v>76.10502200906323</v>
       </c>
-      <c r="AT20" t="n">
+      <c r="BC20" t="n">
         <v>74.20934914146599</v>
       </c>
-      <c r="AU20" t="n">
+      <c r="BD20" t="n">
         <v>71.61878245264995</v>
       </c>
-      <c r="AV20" t="n">
+      <c r="BE20" t="n">
         <v>69.79540386013967</v>
       </c>
-      <c r="AW20" t="n">
+      <c r="BF20" t="n">
         <v>68.6802974941787</v>
       </c>
-      <c r="AX20" t="n">
+      <c r="BG20" t="n">
         <v>67.30717886325806</v>
       </c>
-      <c r="AY20" t="n">
+      <c r="BH20" t="n">
         <v>65.31149371234362</v>
       </c>
-      <c r="AZ20" t="n">
+      <c r="BI20" t="n">
         <v>63.42777826438157</v>
       </c>
-      <c r="BA20" t="n">
+      <c r="BJ20" t="n">
         <v>62.23749593291812</v>
       </c>
-      <c r="BB20" t="n">
+      <c r="BK20" t="n">
         <v>317</v>
       </c>
-      <c r="BC20" t="n">
+      <c r="BL20" t="n">
         <v>317</v>
       </c>
-      <c r="BD20" t="n">
+      <c r="BM20" t="n">
         <v>317</v>
       </c>
-      <c r="BE20" t="n">
+      <c r="BN20" t="n">
         <v>317</v>
       </c>
-      <c r="BF20" t="n">
+      <c r="BO20" t="n">
         <v>317</v>
       </c>
-      <c r="BG20" t="n">
+      <c r="BP20" t="n">
         <v>317</v>
       </c>
-      <c r="BH20" t="n">
+      <c r="BQ20" t="n">
         <v>317</v>
       </c>
-      <c r="BI20" t="n">
+      <c r="BR20" t="n">
         <v>317</v>
       </c>
-      <c r="BJ20" t="n">
+      <c r="BS20" t="n">
         <v>317</v>
       </c>
-      <c r="BK20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS20" t="n">
-        <v>669</v>
-      </c>
       <c r="BT20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ20" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA20" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB20" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC20" t="n">
         <v>0.7777777777777778</v>
       </c>
-      <c r="BU20" t="n">
+      <c r="CD20" t="n">
         <v>0.5294117647058824</v>
       </c>
-      <c r="BV20" t="n">
+      <c r="CE20" t="n">
         <v>0.5909090909090909</v>
       </c>
-      <c r="BW20" t="n">
+      <c r="CF20" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="BX20" t="n">
+      <c r="CG20" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="BY20" t="n">
+      <c r="CH20" t="n">
         <v>0.5555555555555556</v>
       </c>
-      <c r="BZ20" t="n">
+      <c r="CI20" t="n">
         <v>0.4347826086956522</v>
       </c>
-      <c r="CA20" t="n">
+      <c r="CJ20" t="n">
         <v>0.5106382978723404</v>
       </c>
-      <c r="CB20" t="n">
+      <c r="CK20" t="n">
         <v>0.02127659574468085</v>
+      </c>
+      <c r="CL20" t="n">
+        <v>500.26</v>
+      </c>
+      <c r="CM20" t="n">
+        <v>52.13</v>
       </c>
     </row>
     <row r="21">
@@ -5514,10 +6196,10 @@
         <v>500</v>
       </c>
       <c r="C21" t="n">
+        <v>62.26834692364714</v>
+      </c>
+      <c r="D21" t="n">
         <v>42</v>
-      </c>
-      <c r="D21" t="n">
-        <v>62.26834692364714</v>
       </c>
       <c r="E21" t="n">
         <v>500</v>
@@ -5526,228 +6208,261 @@
         <v>200</v>
       </c>
       <c r="G21" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="H21" t="inlineStr">
+        <v>77.5</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="M21" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Q21" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I21" t="n">
-        <v>486.1016020772956</v>
-      </c>
-      <c r="J21" t="n">
-        <v>39.05225665533936</v>
-      </c>
-      <c r="K21" t="n">
-        <v>502.5946936450993</v>
-      </c>
-      <c r="L21" t="n">
-        <v>39.96374098016763</v>
-      </c>
-      <c r="M21" t="n">
-        <v>500.6595395516247</v>
-      </c>
-      <c r="N21" t="n">
-        <v>42.84086615920017</v>
-      </c>
-      <c r="O21" t="n">
-        <v>499.2654668397479</v>
-      </c>
-      <c r="P21" t="n">
-        <v>36.74747260281983</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>499.9807131600516</v>
-      </c>
       <c r="R21" t="n">
-        <v>40.29828590785359</v>
+        <v>486.1</v>
       </c>
       <c r="S21" t="n">
-        <v>496.7000822850191</v>
+        <v>39.05</v>
       </c>
       <c r="T21" t="n">
-        <v>43.05625434308097</v>
+        <v>502.59</v>
       </c>
       <c r="U21" t="n">
-        <v>496.1539206500569</v>
+        <v>39.96</v>
       </c>
       <c r="V21" t="n">
-        <v>45.84607366123949</v>
+        <v>500.66</v>
       </c>
       <c r="W21" t="n">
-        <v>500.1210409621164</v>
+        <v>42.84</v>
       </c>
       <c r="X21" t="n">
-        <v>49.57670109540751</v>
+        <v>499.27</v>
       </c>
       <c r="Y21" t="n">
-        <v>499.7956069495724</v>
+        <v>36.75</v>
       </c>
       <c r="Z21" t="n">
-        <v>52.52188248659039</v>
+        <v>499.98</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>40.3</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>496.7</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>43.06</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>496.15</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>45.85</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>500.12</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>49.58</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>499.8</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>52.52</v>
       </c>
       <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
         <v>497.95</v>
       </c>
-      <c r="AK21" t="n">
+      <c r="AT21" t="n">
         <v>495.7666666666667</v>
       </c>
-      <c r="AL21" t="n">
+      <c r="AU21" t="n">
         <v>498.15</v>
       </c>
-      <c r="AM21" t="n">
+      <c r="AV21" t="n">
         <v>499.2</v>
       </c>
-      <c r="AN21" t="n">
+      <c r="AW21" t="n">
         <v>499.925</v>
       </c>
-      <c r="AO21" t="n">
+      <c r="AX21" t="n">
         <v>499.6571428571428</v>
       </c>
-      <c r="AP21" t="n">
+      <c r="AY21" t="n">
         <v>496.95</v>
       </c>
-      <c r="AQ21" t="n">
+      <c r="AZ21" t="n">
         <v>495.7</v>
       </c>
-      <c r="AR21" t="n">
+      <c r="BA21" t="n">
         <v>495.625</v>
       </c>
-      <c r="AS21" t="n">
+      <c r="BB21" t="n">
         <v>69.32025317322493</v>
       </c>
-      <c r="AT21" t="n">
+      <c r="BC21" t="n">
         <v>62.77429587197472</v>
       </c>
-      <c r="AU21" t="n">
+      <c r="BD21" t="n">
         <v>59.60601899137368</v>
       </c>
-      <c r="AV21" t="n">
+      <c r="BE21" t="n">
         <v>56.32974347536122</v>
       </c>
-      <c r="AW21" t="n">
+      <c r="BF21" t="n">
         <v>55.0348620573057</v>
       </c>
-      <c r="AX21" t="n">
+      <c r="BG21" t="n">
         <v>53.8184476376126</v>
       </c>
-      <c r="AY21" t="n">
+      <c r="BH21" t="n">
         <v>55.28254697461035</v>
       </c>
-      <c r="AZ21" t="n">
+      <c r="BI21" t="n">
         <v>56.24558254259223</v>
       </c>
-      <c r="BA21" t="n">
+      <c r="BJ21" t="n">
         <v>58.57545881169007</v>
       </c>
-      <c r="BB21" t="n">
+      <c r="BK21" t="n">
         <v>343</v>
       </c>
-      <c r="BC21" t="n">
+      <c r="BL21" t="n">
         <v>343</v>
       </c>
-      <c r="BD21" t="n">
+      <c r="BM21" t="n">
         <v>343</v>
       </c>
-      <c r="BE21" t="n">
+      <c r="BN21" t="n">
         <v>343</v>
       </c>
-      <c r="BF21" t="n">
+      <c r="BO21" t="n">
         <v>343</v>
       </c>
-      <c r="BG21" t="n">
+      <c r="BP21" t="n">
         <v>343</v>
       </c>
-      <c r="BH21" t="n">
+      <c r="BQ21" t="n">
         <v>343</v>
       </c>
-      <c r="BI21" t="n">
+      <c r="BR21" t="n">
         <v>343</v>
       </c>
-      <c r="BJ21" t="n">
+      <c r="BS21" t="n">
         <v>343</v>
       </c>
-      <c r="BK21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS21" t="n">
-        <v>669</v>
-      </c>
       <c r="BT21" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW21" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX21" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY21" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ21" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA21" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB21" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC21" t="n">
         <v>0.8</v>
       </c>
-      <c r="BU21" t="n">
+      <c r="CD21" t="n">
         <v>0.625</v>
       </c>
-      <c r="BV21" t="n">
+      <c r="CE21" t="n">
         <v>0.9375</v>
       </c>
-      <c r="BW21" t="n">
+      <c r="CF21" t="n">
         <v>1</v>
       </c>
-      <c r="BX21" t="n">
+      <c r="CG21" t="n">
         <v>0.9642857142857143</v>
       </c>
-      <c r="BY21" t="n">
+      <c r="CH21" t="n">
         <v>0.9090909090909091</v>
       </c>
-      <c r="BZ21" t="n">
+      <c r="CI21" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="CA21" t="n">
+      <c r="CJ21" t="n">
         <v>0.7692307692307693</v>
       </c>
-      <c r="CB21" t="n">
+      <c r="CK21" t="n">
         <v>0.7692307692307693</v>
+      </c>
+      <c r="CL21" t="n">
+        <v>499.8</v>
+      </c>
+      <c r="CM21" t="n">
+        <v>52.52</v>
       </c>
     </row>
     <row r="22">
@@ -5760,10 +6475,10 @@
         <v>499.9</v>
       </c>
       <c r="C22" t="n">
+        <v>60.34099332839141</v>
+      </c>
+      <c r="D22" t="n">
         <v>40.7</v>
-      </c>
-      <c r="D22" t="n">
-        <v>60.34099332839141</v>
       </c>
       <c r="E22" t="n">
         <v>499.9</v>
@@ -5772,224 +6487,239 @@
         <v>200</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5029999999999999</v>
-      </c>
-      <c r="H22" t="inlineStr"/>
+        <v>79.8</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.3205</v>
+      </c>
       <c r="I22" t="n">
-        <v>490.9703190246008</v>
+        <v>2.3</v>
       </c>
       <c r="J22" t="n">
-        <v>46.58627401765624</v>
+        <v>2.298999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>495.652503782718</v>
+        <v>2.32</v>
       </c>
       <c r="L22" t="n">
-        <v>47.51389866278385</v>
+        <v>2.350499999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>495.7754270823822</v>
+        <v>2.3785</v>
       </c>
       <c r="N22" t="n">
-        <v>47.27579464596054</v>
+        <v>2.612000000000001</v>
       </c>
       <c r="O22" t="n">
-        <v>496.7846958984194</v>
+        <v>2.458999999999999</v>
       </c>
       <c r="P22" t="n">
-        <v>46.53154991125063</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>496.3969073095781</v>
-      </c>
+        <v>2.3785</v>
+      </c>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="n">
-        <v>48.90970918963767</v>
+        <v>490.97</v>
       </c>
       <c r="S22" t="n">
-        <v>496.6359052075451</v>
+        <v>46.58649999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>48.88281567051455</v>
+        <v>495.652</v>
       </c>
       <c r="U22" t="n">
-        <v>496.5672476640351</v>
+        <v>47.51450000000001</v>
       </c>
       <c r="V22" t="n">
-        <v>49.34508790036928</v>
+        <v>495.776</v>
       </c>
       <c r="W22" t="n">
-        <v>496.7294234038915</v>
+        <v>47.27499999999999</v>
       </c>
       <c r="X22" t="n">
-        <v>49.6686651321</v>
+        <v>496.7855</v>
       </c>
       <c r="Y22" t="n">
-        <v>496.6442341782875</v>
+        <v>46.531</v>
       </c>
       <c r="Z22" t="n">
-        <v>49.87183574681049</v>
+        <v>496.397</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>48.909</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>496.6355</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>48.88249999999999</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>496.566</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>49.34650000000001</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>496.7285000000001</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>49.6685</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>496.6435</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>49.8725</v>
       </c>
       <c r="AJ22" t="n">
-        <v>498.4400000000001</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>496.6466666666666</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>496.6074999999999</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>498.4395000000001</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>496.6465</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>496.6065</v>
+      </c>
+      <c r="AV22" t="n">
         <v>496.5310000000001</v>
       </c>
-      <c r="AN22" t="n">
-        <v>496.6258333333333</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>496.4828571428571</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>496.29625</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>496.4363888888889</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>496.9075</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>81.75001595423913</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>74.554831850556</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>69.72465687015605</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>66.36486290686054</v>
-      </c>
       <c r="AW22" t="n">
-        <v>64.48564017204876</v>
+        <v>496.626</v>
       </c>
       <c r="AX22" t="n">
-        <v>63.70577551352828</v>
+        <v>496.4825</v>
       </c>
       <c r="AY22" t="n">
-        <v>63.31655486118075</v>
+        <v>496.297</v>
       </c>
       <c r="AZ22" t="n">
-        <v>62.8886346451181</v>
+        <v>496.4365000000001</v>
       </c>
       <c r="BA22" t="n">
-        <v>62.61442716021507</v>
+        <v>496.9059999999999</v>
       </c>
       <c r="BB22" t="n">
+        <v>81.74999999999999</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>74.554</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>69.72399999999999</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>66.36549999999998</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>64.486</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>63.706</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>63.31599999999999</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>62.889</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>62.6145</v>
+      </c>
+      <c r="BK22" t="n">
         <v>328.5</v>
       </c>
-      <c r="BC22" t="n">
+      <c r="BL22" t="n">
         <v>328.5</v>
       </c>
-      <c r="BD22" t="n">
+      <c r="BM22" t="n">
         <v>328.5</v>
       </c>
-      <c r="BE22" t="n">
+      <c r="BN22" t="n">
         <v>328.5</v>
       </c>
-      <c r="BF22" t="n">
+      <c r="BO22" t="n">
         <v>328.5</v>
       </c>
-      <c r="BG22" t="n">
+      <c r="BP22" t="n">
         <v>328.5</v>
       </c>
-      <c r="BH22" t="n">
+      <c r="BQ22" t="n">
         <v>328.5</v>
       </c>
-      <c r="BI22" t="n">
+      <c r="BR22" t="n">
         <v>328.5</v>
       </c>
-      <c r="BJ22" t="n">
+      <c r="BS22" t="n">
         <v>328.5</v>
       </c>
-      <c r="BK22" t="n">
+      <c r="BT22" t="n">
         <v>669.3</v>
       </c>
-      <c r="BL22" t="n">
+      <c r="BU22" t="n">
         <v>669.3</v>
       </c>
-      <c r="BM22" t="n">
+      <c r="BV22" t="n">
         <v>669.3</v>
       </c>
-      <c r="BN22" t="n">
+      <c r="BW22" t="n">
         <v>669.3</v>
       </c>
-      <c r="BO22" t="n">
+      <c r="BX22" t="n">
         <v>669.3</v>
       </c>
-      <c r="BP22" t="n">
+      <c r="BY22" t="n">
         <v>669.3</v>
       </c>
-      <c r="BQ22" t="n">
+      <c r="BZ22" t="n">
         <v>669.3</v>
       </c>
-      <c r="BR22" t="n">
+      <c r="CA22" t="n">
         <v>669.3</v>
       </c>
-      <c r="BS22" t="n">
+      <c r="CB22" t="n">
         <v>669.3</v>
       </c>
-      <c r="BT22" t="n">
-        <v>0.615157203907204</v>
-      </c>
-      <c r="BU22" t="n">
-        <v>0.6862549239116578</v>
-      </c>
-      <c r="BV22" t="n">
-        <v>0.6984890046600574</v>
-      </c>
-      <c r="BW22" t="n">
-        <v>0.705077521759444</v>
-      </c>
-      <c r="BX22" t="n">
-        <v>0.6952608797102559</v>
-      </c>
-      <c r="BY22" t="n">
-        <v>0.6566549169662474</v>
-      </c>
-      <c r="BZ22" t="n">
-        <v>0.6147076352800804</v>
-      </c>
-      <c r="CA22" t="n">
-        <v>0.6249821724894071</v>
-      </c>
-      <c r="CB22" t="n">
-        <v>0.6476482576497944</v>
+      <c r="CC22" t="inlineStr"/>
+      <c r="CD22" t="inlineStr"/>
+      <c r="CE22" t="inlineStr"/>
+      <c r="CF22" t="inlineStr"/>
+      <c r="CG22" t="inlineStr"/>
+      <c r="CH22" t="inlineStr"/>
+      <c r="CI22" t="inlineStr"/>
+      <c r="CJ22" t="inlineStr"/>
+      <c r="CK22" t="inlineStr"/>
+      <c r="CL22" t="n">
+        <v>496.6435</v>
+      </c>
+      <c r="CM22" t="n">
+        <v>49.8725</v>
       </c>
     </row>
     <row r="23">
@@ -6002,10 +6732,10 @@
         <v>1.410487037944882</v>
       </c>
       <c r="C23" t="n">
+        <v>1.930052761342485</v>
+      </c>
+      <c r="D23" t="n">
         <v>1.30182058752551</v>
-      </c>
-      <c r="D23" t="n">
-        <v>1.930052761342485</v>
       </c>
       <c r="E23" t="n">
         <v>1.410487037944882</v>
@@ -6014,224 +6744,239 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.01657518754359249</v>
-      </c>
-      <c r="H23" t="inlineStr"/>
+        <v>1.196486083232238</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.2741585211822571</v>
+      </c>
       <c r="I23" t="n">
-        <v>19.42319593180319</v>
+        <v>0.3054074069346163</v>
       </c>
       <c r="J23" t="n">
-        <v>9.166656520615209</v>
+        <v>0.323498962822709</v>
       </c>
       <c r="K23" t="n">
-        <v>12.05519092712915</v>
+        <v>0.3348841119268764</v>
       </c>
       <c r="L23" t="n">
-        <v>7.608624873717989</v>
+        <v>0.3174151357781362</v>
       </c>
       <c r="M23" t="n">
-        <v>10.74247387762475</v>
+        <v>0.2975562750844036</v>
       </c>
       <c r="N23" t="n">
-        <v>7.295432954760283</v>
+        <v>0.1842938157571105</v>
       </c>
       <c r="O23" t="n">
-        <v>8.653311317496385</v>
+        <v>0.2041645363297379</v>
       </c>
       <c r="P23" t="n">
-        <v>6.619638865236117</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>7.409919336225998</v>
-      </c>
+        <v>0.2509618339613878</v>
+      </c>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="n">
-        <v>6.967031136985633</v>
+        <v>19.42357113894028</v>
       </c>
       <c r="S23" t="n">
-        <v>7.651087567706266</v>
+        <v>9.167319113941769</v>
       </c>
       <c r="T23" t="n">
-        <v>6.23065252281085</v>
+        <v>12.05508436085655</v>
       </c>
       <c r="U23" t="n">
-        <v>6.338717394652106</v>
+        <v>7.60906694259172</v>
       </c>
       <c r="V23" t="n">
-        <v>5.140392814364761</v>
+        <v>10.74240706144038</v>
       </c>
       <c r="W23" t="n">
-        <v>6.071786953488472</v>
+        <v>7.294174676447384</v>
       </c>
       <c r="X23" t="n">
-        <v>5.166347226427065</v>
+        <v>8.653032005877298</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.091014039403206</v>
+        <v>6.61876431463091</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.784051141029718</v>
+        <v>7.411007531474985</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>6.967232252706801</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>7.651523738858551</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>6.2304058117387</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>6.339677395079669</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>5.13993986755733</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>6.070956115629133</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>5.165864960437283</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>5.091008870134631</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>4.783365777137971</v>
       </c>
       <c r="AJ23" t="n">
-        <v>12.84362272635109</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>12.88062101223458</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>11.78165277477073</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>12.84340030193677</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>12.88096607810389</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>11.78272699871791</v>
+      </c>
+      <c r="AV23" t="n">
         <v>10.27155648534237</v>
       </c>
-      <c r="AN23" t="n">
-        <v>8.343311526140097</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>6.89798940179856</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>5.981588871498244</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>5.563909647186339</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>5.261016886896538</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>7.40611972995079</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>6.78664779249692</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>5.987811575367462</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>5.625915724629949</v>
-      </c>
       <c r="AW23" t="n">
-        <v>5.213114977361037</v>
+        <v>8.342363290049041</v>
       </c>
       <c r="AX23" t="n">
-        <v>5.178833324520074</v>
+        <v>6.898670257070524</v>
       </c>
       <c r="AY23" t="n">
-        <v>4.908645036789624</v>
+        <v>5.982164807949856</v>
       </c>
       <c r="AZ23" t="n">
-        <v>4.904791196073059</v>
+        <v>5.564050280714204</v>
       </c>
       <c r="BA23" t="n">
-        <v>4.767827641502537</v>
+        <v>5.261306021572174</v>
       </c>
       <c r="BB23" t="n">
+        <v>7.406078584514212</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>6.785916840665013</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>5.986916788429494</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>5.625190031877755</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>5.21381403984696</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>5.178646846222933</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>4.908845292455565</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>4.904186074429843</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>4.767090555928327</v>
+      </c>
+      <c r="BK23" t="n">
         <v>8.482179461733443</v>
       </c>
-      <c r="BC23" t="n">
+      <c r="BL23" t="n">
         <v>8.482179461733443</v>
       </c>
-      <c r="BD23" t="n">
+      <c r="BM23" t="n">
         <v>8.482179461733443</v>
       </c>
-      <c r="BE23" t="n">
+      <c r="BN23" t="n">
         <v>8.482179461733443</v>
       </c>
-      <c r="BF23" t="n">
+      <c r="BO23" t="n">
         <v>8.482179461733443</v>
       </c>
-      <c r="BG23" t="n">
+      <c r="BP23" t="n">
         <v>8.482179461733443</v>
       </c>
-      <c r="BH23" t="n">
+      <c r="BQ23" t="n">
         <v>8.482179461733443</v>
       </c>
-      <c r="BI23" t="n">
+      <c r="BR23" t="n">
         <v>8.482179461733443</v>
       </c>
-      <c r="BJ23" t="n">
+      <c r="BS23" t="n">
         <v>8.482179461733443</v>
       </c>
-      <c r="BK23" t="n">
+      <c r="BT23" t="n">
         <v>1.341640786499874</v>
       </c>
-      <c r="BL23" t="n">
+      <c r="BU23" t="n">
         <v>1.341640786499874</v>
       </c>
-      <c r="BM23" t="n">
+      <c r="BV23" t="n">
         <v>1.341640786499874</v>
       </c>
-      <c r="BN23" t="n">
+      <c r="BW23" t="n">
         <v>1.341640786499874</v>
       </c>
-      <c r="BO23" t="n">
+      <c r="BX23" t="n">
         <v>1.341640786499874</v>
       </c>
-      <c r="BP23" t="n">
+      <c r="BY23" t="n">
         <v>1.341640786499874</v>
       </c>
-      <c r="BQ23" t="n">
+      <c r="BZ23" t="n">
         <v>1.341640786499874</v>
       </c>
-      <c r="BR23" t="n">
+      <c r="CA23" t="n">
         <v>1.341640786499874</v>
       </c>
-      <c r="BS23" t="n">
+      <c r="CB23" t="n">
         <v>1.341640786499874</v>
       </c>
-      <c r="BT23" t="n">
-        <v>0.312961795333177</v>
-      </c>
-      <c r="BU23" t="n">
-        <v>0.2015920555191223</v>
-      </c>
-      <c r="BV23" t="n">
-        <v>0.1800003037013406</v>
-      </c>
-      <c r="BW23" t="n">
-        <v>0.1827137791789849</v>
-      </c>
-      <c r="BX23" t="n">
-        <v>0.1590334073903081</v>
-      </c>
-      <c r="BY23" t="n">
-        <v>0.2120089786583293</v>
-      </c>
-      <c r="BZ23" t="n">
-        <v>0.2454449425266253</v>
-      </c>
-      <c r="CA23" t="n">
-        <v>0.251790157073075</v>
-      </c>
-      <c r="CB23" t="n">
-        <v>0.2325150152195486</v>
+      <c r="CC23" t="inlineStr"/>
+      <c r="CD23" t="inlineStr"/>
+      <c r="CE23" t="inlineStr"/>
+      <c r="CF23" t="inlineStr"/>
+      <c r="CG23" t="inlineStr"/>
+      <c r="CH23" t="inlineStr"/>
+      <c r="CI23" t="inlineStr"/>
+      <c r="CJ23" t="inlineStr"/>
+      <c r="CK23" t="inlineStr"/>
+      <c r="CL23" t="n">
+        <v>5.091008870134631</v>
+      </c>
+      <c r="CM23" t="n">
+        <v>4.783365777137971</v>
       </c>
     </row>
   </sheetData>
